--- a/docs/timelines/mordrienne/mordrienne_s2_sync_sheet.xlsx
+++ b/docs/timelines/mordrienne/mordrienne_s2_sync_sheet.xlsx
@@ -80,7 +80,7 @@
       <i val="1"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -110,6 +110,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0099E0B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B4FFD0"/>
       </patternFill>
     </fill>
     <fill>
@@ -154,6 +159,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00A7FFC7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00DBDBDB"/>
       </patternFill>
     </fill>
@@ -183,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -204,46 +214,51 @@
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -665,7 +680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U123"/>
+  <dimension ref="A1:V123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -686,9 +701,10 @@
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
     <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="34" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="34" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -782,21 +798,27 @@
       </c>
       <c r="R1" s="3" t="inlineStr">
         <is>
+          <t>tip
+Wand Flash</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
           <t>events
 อีเวนต์</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>Shake dx</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Shake dy</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -859,13 +881,14 @@
       <c r="P2" s="6" t="inlineStr"/>
       <c r="Q2" s="6" t="inlineStr"/>
       <c r="R2" s="6" t="inlineStr"/>
-      <c r="S2" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S2" s="6" t="inlineStr"/>
       <c r="T2" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U2" s="6" t="inlineStr">
+      <c r="U2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="6" t="inlineStr">
         <is>
           <t>C01</t>
         </is>
@@ -924,13 +947,14 @@
       <c r="P3" s="6" t="inlineStr"/>
       <c r="Q3" s="6" t="inlineStr"/>
       <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S3" s="6" t="inlineStr"/>
       <c r="T3" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U3" s="6" t="inlineStr"/>
+      <c r="U3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -985,13 +1009,14 @@
       <c r="P4" s="6" t="inlineStr"/>
       <c r="Q4" s="6" t="inlineStr"/>
       <c r="R4" s="6" t="inlineStr"/>
-      <c r="S4" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S4" s="6" t="inlineStr"/>
       <c r="T4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U4" s="6" t="inlineStr"/>
+      <c r="U4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="n">
@@ -1050,13 +1075,14 @@
       <c r="P5" s="6" t="inlineStr"/>
       <c r="Q5" s="6" t="inlineStr"/>
       <c r="R5" s="6" t="inlineStr"/>
-      <c r="S5" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S5" s="6" t="inlineStr"/>
       <c r="T5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U5" s="6" t="inlineStr">
+      <c r="U5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="6" t="inlineStr">
         <is>
           <t>C02 เริ่มท่า</t>
         </is>
@@ -1115,13 +1141,14 @@
       <c r="P6" s="6" t="inlineStr"/>
       <c r="Q6" s="6" t="inlineStr"/>
       <c r="R6" s="6" t="inlineStr"/>
-      <c r="S6" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S6" s="6" t="inlineStr"/>
       <c r="T6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U6" s="6" t="inlineStr"/>
+      <c r="U6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
@@ -1176,13 +1203,14 @@
       <c r="P7" s="6" t="inlineStr"/>
       <c r="Q7" s="6" t="inlineStr"/>
       <c r="R7" s="6" t="inlineStr"/>
-      <c r="S7" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S7" s="6" t="inlineStr"/>
       <c r="T7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U7" s="6" t="inlineStr"/>
+      <c r="U7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
@@ -1237,13 +1265,14 @@
       <c r="P8" s="6" t="inlineStr"/>
       <c r="Q8" s="6" t="inlineStr"/>
       <c r="R8" s="6" t="inlineStr"/>
-      <c r="S8" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S8" s="6" t="inlineStr"/>
       <c r="T8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U8" s="6" t="inlineStr"/>
+      <c r="U8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="n">
@@ -1298,13 +1327,14 @@
       <c r="P9" s="6" t="inlineStr"/>
       <c r="Q9" s="6" t="inlineStr"/>
       <c r="R9" s="6" t="inlineStr"/>
-      <c r="S9" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S9" s="6" t="inlineStr"/>
       <c r="T9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U9" s="6" t="inlineStr"/>
+      <c r="U9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
@@ -1359,13 +1389,14 @@
       <c r="P10" s="6" t="inlineStr"/>
       <c r="Q10" s="6" t="inlineStr"/>
       <c r="R10" s="6" t="inlineStr"/>
-      <c r="S10" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S10" s="6" t="inlineStr"/>
       <c r="T10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U10" s="6" t="inlineStr"/>
+      <c r="U10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n">
@@ -1420,13 +1451,14 @@
       <c r="P11" s="6" t="inlineStr"/>
       <c r="Q11" s="6" t="inlineStr"/>
       <c r="R11" s="6" t="inlineStr"/>
-      <c r="S11" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S11" s="6" t="inlineStr"/>
       <c r="T11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U11" s="6" t="inlineStr"/>
+      <c r="U11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
@@ -1481,13 +1513,14 @@
       <c r="P12" s="6" t="inlineStr"/>
       <c r="Q12" s="6" t="inlineStr"/>
       <c r="R12" s="6" t="inlineStr"/>
-      <c r="S12" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S12" s="6" t="inlineStr"/>
       <c r="T12" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U12" s="6" t="inlineStr"/>
+      <c r="U12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
@@ -1542,13 +1575,14 @@
       <c r="P13" s="6" t="inlineStr"/>
       <c r="Q13" s="6" t="inlineStr"/>
       <c r="R13" s="6" t="inlineStr"/>
-      <c r="S13" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S13" s="6" t="inlineStr"/>
       <c r="T13" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U13" s="6" t="inlineStr"/>
+      <c r="U13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
@@ -1603,13 +1637,14 @@
       <c r="P14" s="6" t="inlineStr"/>
       <c r="Q14" s="6" t="inlineStr"/>
       <c r="R14" s="6" t="inlineStr"/>
-      <c r="S14" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S14" s="6" t="inlineStr"/>
       <c r="T14" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U14" s="6" t="inlineStr"/>
+      <c r="U14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="n">
@@ -1664,13 +1699,14 @@
       <c r="P15" s="6" t="inlineStr"/>
       <c r="Q15" s="6" t="inlineStr"/>
       <c r="R15" s="6" t="inlineStr"/>
-      <c r="S15" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S15" s="6" t="inlineStr"/>
       <c r="T15" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U15" s="6" t="inlineStr"/>
+      <c r="U15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
@@ -1725,13 +1761,14 @@
       <c r="P16" s="6" t="inlineStr"/>
       <c r="Q16" s="6" t="inlineStr"/>
       <c r="R16" s="6" t="inlineStr"/>
-      <c r="S16" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S16" s="6" t="inlineStr"/>
       <c r="T16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U16" s="6" t="inlineStr"/>
+      <c r="U16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="n">
@@ -1786,13 +1823,14 @@
       <c r="P17" s="6" t="inlineStr"/>
       <c r="Q17" s="6" t="inlineStr"/>
       <c r="R17" s="6" t="inlineStr"/>
-      <c r="S17" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S17" s="6" t="inlineStr"/>
       <c r="T17" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U17" s="6" t="inlineStr"/>
+      <c r="U17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
@@ -1847,13 +1885,14 @@
       <c r="P18" s="6" t="inlineStr"/>
       <c r="Q18" s="6" t="inlineStr"/>
       <c r="R18" s="6" t="inlineStr"/>
-      <c r="S18" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S18" s="6" t="inlineStr"/>
       <c r="T18" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U18" s="6" t="inlineStr"/>
+      <c r="U18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="n">
@@ -1908,13 +1947,14 @@
       <c r="P19" s="6" t="inlineStr"/>
       <c r="Q19" s="6" t="inlineStr"/>
       <c r="R19" s="6" t="inlineStr"/>
-      <c r="S19" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S19" s="6" t="inlineStr"/>
       <c r="T19" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U19" s="6" t="inlineStr"/>
+      <c r="U19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
@@ -1969,13 +2009,14 @@
       <c r="P20" s="6" t="inlineStr"/>
       <c r="Q20" s="6" t="inlineStr"/>
       <c r="R20" s="6" t="inlineStr"/>
-      <c r="S20" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S20" s="6" t="inlineStr"/>
       <c r="T20" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U20" s="6" t="inlineStr"/>
+      <c r="U20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
@@ -2030,13 +2071,14 @@
       <c r="P21" s="6" t="inlineStr"/>
       <c r="Q21" s="6" t="inlineStr"/>
       <c r="R21" s="6" t="inlineStr"/>
-      <c r="S21" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S21" s="6" t="inlineStr"/>
       <c r="T21" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U21" s="6" t="inlineStr"/>
+      <c r="U21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
@@ -2091,13 +2133,14 @@
       <c r="P22" s="6" t="inlineStr"/>
       <c r="Q22" s="6" t="inlineStr"/>
       <c r="R22" s="6" t="inlineStr"/>
-      <c r="S22" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S22" s="6" t="inlineStr"/>
       <c r="T22" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U22" s="6" t="inlineStr"/>
+      <c r="U22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="n">
@@ -2156,13 +2199,14 @@
       <c r="P23" s="6" t="inlineStr"/>
       <c r="Q23" s="6" t="inlineStr"/>
       <c r="R23" s="6" t="inlineStr"/>
-      <c r="S23" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S23" s="6" t="inlineStr"/>
       <c r="T23" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U23" s="6" t="inlineStr">
+      <c r="U23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="6" t="inlineStr">
         <is>
           <t>C08</t>
         </is>
@@ -2221,13 +2265,14 @@
       <c r="P24" s="6" t="inlineStr"/>
       <c r="Q24" s="6" t="inlineStr"/>
       <c r="R24" s="6" t="inlineStr"/>
-      <c r="S24" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S24" s="6" t="inlineStr"/>
       <c r="T24" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U24" s="6" t="inlineStr"/>
+      <c r="U24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="n">
@@ -2282,13 +2327,14 @@
       <c r="P25" s="6" t="inlineStr"/>
       <c r="Q25" s="6" t="inlineStr"/>
       <c r="R25" s="6" t="inlineStr"/>
-      <c r="S25" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S25" s="6" t="inlineStr"/>
       <c r="T25" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U25" s="6" t="inlineStr"/>
+      <c r="U25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="10" t="n">
@@ -2350,14 +2396,19 @@
       </c>
       <c r="P26" s="6" t="inlineStr"/>
       <c r="Q26" s="6" t="inlineStr"/>
-      <c r="R26" s="6" t="inlineStr"/>
-      <c r="S26" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="R26" s="13" t="inlineStr">
+        <is>
+          <t>f1 · 100% · over</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr"/>
       <c r="T26" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U26" s="6" t="inlineStr">
+      <c r="U26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="6" t="inlineStr">
         <is>
           <t>C09 · วงเฮ็กซ์เกิดบนพื้น (ไม่ติดตัว)</t>
         </is>
@@ -2419,14 +2470,19 @@
       </c>
       <c r="P27" s="6" t="inlineStr"/>
       <c r="Q27" s="6" t="inlineStr"/>
-      <c r="R27" s="6" t="inlineStr"/>
-      <c r="S27" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="R27" s="13" t="inlineStr">
+        <is>
+          <t>f1 · 100% · over</t>
+        </is>
+      </c>
+      <c r="S27" s="6" t="inlineStr"/>
       <c r="T27" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U27" s="6" t="inlineStr"/>
+      <c r="U27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="10" t="n">
@@ -2484,14 +2540,19 @@
       </c>
       <c r="P28" s="6" t="inlineStr"/>
       <c r="Q28" s="6" t="inlineStr"/>
-      <c r="R28" s="6" t="inlineStr"/>
-      <c r="S28" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="R28" s="13" t="inlineStr">
+        <is>
+          <t>f1 · 100% · over</t>
+        </is>
+      </c>
+      <c r="S28" s="6" t="inlineStr"/>
       <c r="T28" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U28" s="6" t="inlineStr"/>
+      <c r="U28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="10" t="n">
@@ -2549,14 +2610,19 @@
       </c>
       <c r="P29" s="6" t="inlineStr"/>
       <c r="Q29" s="6" t="inlineStr"/>
-      <c r="R29" s="6" t="inlineStr"/>
-      <c r="S29" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="R29" s="13" t="inlineStr">
+        <is>
+          <t>f2 · 100% · over</t>
+        </is>
+      </c>
+      <c r="S29" s="6" t="inlineStr"/>
       <c r="T29" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U29" s="6" t="inlineStr"/>
+      <c r="U29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="10" t="n">
@@ -2614,14 +2680,19 @@
       </c>
       <c r="P30" s="6" t="inlineStr"/>
       <c r="Q30" s="6" t="inlineStr"/>
-      <c r="R30" s="6" t="inlineStr"/>
-      <c r="S30" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="R30" s="13" t="inlineStr">
+        <is>
+          <t>f2 · 100% · over</t>
+        </is>
+      </c>
+      <c r="S30" s="6" t="inlineStr"/>
       <c r="T30" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U30" s="6" t="inlineStr"/>
+      <c r="U30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="10" t="n">
@@ -2679,14 +2750,19 @@
       </c>
       <c r="P31" s="6" t="inlineStr"/>
       <c r="Q31" s="6" t="inlineStr"/>
-      <c r="R31" s="6" t="inlineStr"/>
-      <c r="S31" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="R31" s="13" t="inlineStr">
+        <is>
+          <t>f3 · 100% · over</t>
+        </is>
+      </c>
+      <c r="S31" s="6" t="inlineStr"/>
       <c r="T31" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U31" s="6" t="inlineStr"/>
+      <c r="U31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="10" t="n">
@@ -2744,14 +2820,19 @@
       </c>
       <c r="P32" s="6" t="inlineStr"/>
       <c r="Q32" s="6" t="inlineStr"/>
-      <c r="R32" s="6" t="inlineStr"/>
-      <c r="S32" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="R32" s="13" t="inlineStr">
+        <is>
+          <t>f3 · 100% · over</t>
+        </is>
+      </c>
+      <c r="S32" s="6" t="inlineStr"/>
       <c r="T32" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U32" s="6" t="inlineStr"/>
+      <c r="U32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="10" t="n">
@@ -2809,14 +2890,19 @@
       </c>
       <c r="P33" s="6" t="inlineStr"/>
       <c r="Q33" s="6" t="inlineStr"/>
-      <c r="R33" s="6" t="inlineStr"/>
-      <c r="S33" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="R33" s="13" t="inlineStr">
+        <is>
+          <t>f4 · 100% · over</t>
+        </is>
+      </c>
+      <c r="S33" s="6" t="inlineStr"/>
       <c r="T33" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U33" s="6" t="inlineStr"/>
+      <c r="U33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="10" t="n">
@@ -2874,14 +2960,19 @@
       </c>
       <c r="P34" s="6" t="inlineStr"/>
       <c r="Q34" s="6" t="inlineStr"/>
-      <c r="R34" s="6" t="inlineStr"/>
-      <c r="S34" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="R34" s="13" t="inlineStr">
+        <is>
+          <t>f4 · 100% · over</t>
+        </is>
+      </c>
+      <c r="S34" s="6" t="inlineStr"/>
       <c r="T34" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U34" s="6" t="inlineStr"/>
+      <c r="U34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="10" t="n">
@@ -2939,14 +3030,19 @@
       </c>
       <c r="P35" s="6" t="inlineStr"/>
       <c r="Q35" s="6" t="inlineStr"/>
-      <c r="R35" s="6" t="inlineStr"/>
-      <c r="S35" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="R35" s="13" t="inlineStr">
+        <is>
+          <t>f5 · 100% · over</t>
+        </is>
+      </c>
+      <c r="S35" s="6" t="inlineStr"/>
       <c r="T35" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U35" s="6" t="inlineStr"/>
+      <c r="U35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="n">
@@ -3004,14 +3100,19 @@
       </c>
       <c r="P36" s="6" t="inlineStr"/>
       <c r="Q36" s="6" t="inlineStr"/>
-      <c r="R36" s="6" t="inlineStr"/>
-      <c r="S36" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="R36" s="13" t="inlineStr">
+        <is>
+          <t>f5 · 100% · over</t>
+        </is>
+      </c>
+      <c r="S36" s="6" t="inlineStr"/>
       <c r="T36" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U36" s="6" t="inlineStr"/>
+      <c r="U36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="n">
@@ -3069,14 +3170,19 @@
       </c>
       <c r="P37" s="6" t="inlineStr"/>
       <c r="Q37" s="6" t="inlineStr"/>
-      <c r="R37" s="6" t="inlineStr"/>
-      <c r="S37" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="R37" s="13" t="inlineStr">
+        <is>
+          <t>f6 · 100% · over</t>
+        </is>
+      </c>
+      <c r="S37" s="6" t="inlineStr"/>
       <c r="T37" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U37" s="6" t="inlineStr"/>
+      <c r="U37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="10" t="n">
@@ -3134,14 +3240,19 @@
       </c>
       <c r="P38" s="6" t="inlineStr"/>
       <c r="Q38" s="6" t="inlineStr"/>
-      <c r="R38" s="6" t="inlineStr"/>
-      <c r="S38" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="R38" s="13" t="inlineStr">
+        <is>
+          <t>f6 · 100% · over</t>
+        </is>
+      </c>
+      <c r="S38" s="6" t="inlineStr"/>
       <c r="T38" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U38" s="6" t="inlineStr"/>
+      <c r="U38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="n">
@@ -3199,14 +3310,19 @@
       </c>
       <c r="P39" s="6" t="inlineStr"/>
       <c r="Q39" s="6" t="inlineStr"/>
-      <c r="R39" s="6" t="inlineStr"/>
-      <c r="S39" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="R39" s="13" t="inlineStr">
+        <is>
+          <t>f7 · 100% · over</t>
+        </is>
+      </c>
+      <c r="S39" s="6" t="inlineStr"/>
       <c r="T39" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U39" s="6" t="inlineStr"/>
+      <c r="U39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="10" t="n">
@@ -3264,39 +3380,44 @@
       </c>
       <c r="P40" s="6" t="inlineStr"/>
       <c r="Q40" s="6" t="inlineStr"/>
-      <c r="R40" s="6" t="inlineStr"/>
-      <c r="S40" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="R40" s="13" t="inlineStr">
+        <is>
+          <t>f7 · 100% · over</t>
+        </is>
+      </c>
+      <c r="S40" s="6" t="inlineStr"/>
       <c r="T40" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U40" s="6" t="inlineStr"/>
+      <c r="U40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="n">
+      <c r="A41" s="14" t="n">
         <v>39</v>
       </c>
-      <c r="B41" s="14">
+      <c r="B41" s="15">
         <f>A41*1000/60</f>
         <v/>
       </c>
-      <c r="C41" s="13" t="inlineStr">
+      <c r="C41" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D41" s="13" t="inlineStr">
+      <c r="D41" s="14" t="inlineStr">
         <is>
           <t>C13</t>
         </is>
       </c>
-      <c r="E41" s="13" t="inlineStr">
+      <c r="E41" s="14" t="inlineStr">
         <is>
           <t>S2 clip 12</t>
         </is>
       </c>
-      <c r="F41" s="13" t="n">
+      <c r="F41" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="6" t="n">
@@ -3331,49 +3452,54 @@
           <t>f9 · 100% · under</t>
         </is>
       </c>
-      <c r="P41" s="15" t="inlineStr">
+      <c r="P41" s="16" t="inlineStr">
         <is>
           <t>f1 · 100% · under</t>
         </is>
       </c>
       <c r="Q41" s="6" t="inlineStr"/>
-      <c r="R41" s="6" t="inlineStr"/>
-      <c r="S41" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="R41" s="13" t="inlineStr">
+        <is>
+          <t>f7 · 100% · over</t>
+        </is>
+      </c>
+      <c r="S41" s="6" t="inlineStr"/>
       <c r="T41" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U41" s="6" t="inlineStr">
+      <c r="U41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="6" t="inlineStr">
         <is>
           <t>C13 ควงไม้ · วงชาร์จ</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="13" t="n">
+      <c r="A42" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="B42" s="14">
+      <c r="B42" s="15">
         <f>A42*1000/60</f>
         <v/>
       </c>
-      <c r="C42" s="13" t="inlineStr">
+      <c r="C42" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D42" s="13" t="inlineStr">
+      <c r="D42" s="14" t="inlineStr">
         <is>
           <t>C13</t>
         </is>
       </c>
-      <c r="E42" s="13" t="inlineStr">
+      <c r="E42" s="14" t="inlineStr">
         <is>
           <t>S2 clip 12</t>
         </is>
       </c>
-      <c r="F42" s="13" t="n">
+      <c r="F42" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G42" s="6" t="n">
@@ -3400,45 +3526,50 @@
       </c>
       <c r="N42" s="6" t="inlineStr"/>
       <c r="O42" s="6" t="inlineStr"/>
-      <c r="P42" s="15" t="inlineStr">
+      <c r="P42" s="16" t="inlineStr">
         <is>
           <t>f1 · 100% · under</t>
         </is>
       </c>
       <c r="Q42" s="6" t="inlineStr"/>
-      <c r="R42" s="6" t="inlineStr"/>
-      <c r="S42" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="R42" s="13" t="inlineStr">
+        <is>
+          <t>f7 · 93% · over</t>
+        </is>
+      </c>
+      <c r="S42" s="6" t="inlineStr"/>
       <c r="T42" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U42" s="6" t="inlineStr"/>
+      <c r="U42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="13" t="n">
+      <c r="A43" s="14" t="n">
         <v>41</v>
       </c>
-      <c r="B43" s="14">
+      <c r="B43" s="15">
         <f>A43*1000/60</f>
         <v/>
       </c>
-      <c r="C43" s="13" t="inlineStr">
+      <c r="C43" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D43" s="13" t="inlineStr">
+      <c r="D43" s="14" t="inlineStr">
         <is>
           <t>C13</t>
         </is>
       </c>
-      <c r="E43" s="13" t="inlineStr">
+      <c r="E43" s="14" t="inlineStr">
         <is>
           <t>S2 clip 12</t>
         </is>
       </c>
-      <c r="F43" s="13" t="n">
+      <c r="F43" s="14" t="n">
         <v>3</v>
       </c>
       <c r="G43" s="6" t="n">
@@ -3465,45 +3596,50 @@
       </c>
       <c r="N43" s="6" t="inlineStr"/>
       <c r="O43" s="6" t="inlineStr"/>
-      <c r="P43" s="15" t="inlineStr">
+      <c r="P43" s="16" t="inlineStr">
         <is>
           <t>f1 · 100% · under</t>
         </is>
       </c>
       <c r="Q43" s="6" t="inlineStr"/>
-      <c r="R43" s="6" t="inlineStr"/>
-      <c r="S43" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="R43" s="13" t="inlineStr">
+        <is>
+          <t>f7 · 77% · over</t>
+        </is>
+      </c>
+      <c r="S43" s="6" t="inlineStr"/>
       <c r="T43" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U43" s="6" t="inlineStr"/>
+      <c r="U43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="13" t="n">
+      <c r="A44" s="14" t="n">
         <v>42</v>
       </c>
-      <c r="B44" s="14">
+      <c r="B44" s="15">
         <f>A44*1000/60</f>
         <v/>
       </c>
-      <c r="C44" s="13" t="inlineStr">
+      <c r="C44" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D44" s="13" t="inlineStr">
+      <c r="D44" s="14" t="inlineStr">
         <is>
           <t>C13</t>
         </is>
       </c>
-      <c r="E44" s="13" t="inlineStr">
+      <c r="E44" s="14" t="inlineStr">
         <is>
           <t>S2 clip 12</t>
         </is>
       </c>
-      <c r="F44" s="13" t="n">
+      <c r="F44" s="14" t="n">
         <v>4</v>
       </c>
       <c r="G44" s="6" t="n">
@@ -3530,45 +3666,50 @@
       </c>
       <c r="N44" s="6" t="inlineStr"/>
       <c r="O44" s="6" t="inlineStr"/>
-      <c r="P44" s="15" t="inlineStr">
+      <c r="P44" s="16" t="inlineStr">
         <is>
           <t>f1 · 100% · under</t>
         </is>
       </c>
       <c r="Q44" s="6" t="inlineStr"/>
-      <c r="R44" s="6" t="inlineStr"/>
-      <c r="S44" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="R44" s="13" t="inlineStr">
+        <is>
+          <t>f7 · 53% · over</t>
+        </is>
+      </c>
+      <c r="S44" s="6" t="inlineStr"/>
       <c r="T44" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U44" s="6" t="inlineStr"/>
+      <c r="U44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="13" t="n">
+      <c r="A45" s="14" t="n">
         <v>43</v>
       </c>
-      <c r="B45" s="14">
+      <c r="B45" s="15">
         <f>A45*1000/60</f>
         <v/>
       </c>
-      <c r="C45" s="13" t="inlineStr">
+      <c r="C45" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D45" s="13" t="inlineStr">
+      <c r="D45" s="14" t="inlineStr">
         <is>
           <t>C13</t>
         </is>
       </c>
-      <c r="E45" s="13" t="inlineStr">
+      <c r="E45" s="14" t="inlineStr">
         <is>
           <t>S2 clip 12</t>
         </is>
       </c>
-      <c r="F45" s="13" t="n">
+      <c r="F45" s="14" t="n">
         <v>5</v>
       </c>
       <c r="G45" s="6" t="n">
@@ -3595,45 +3736,50 @@
       </c>
       <c r="N45" s="6" t="inlineStr"/>
       <c r="O45" s="6" t="inlineStr"/>
-      <c r="P45" s="15" t="inlineStr">
+      <c r="P45" s="16" t="inlineStr">
         <is>
           <t>f1 · 100% · under</t>
         </is>
       </c>
       <c r="Q45" s="6" t="inlineStr"/>
-      <c r="R45" s="6" t="inlineStr"/>
-      <c r="S45" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="R45" s="13" t="inlineStr">
+        <is>
+          <t>f7 · 20% · over</t>
+        </is>
+      </c>
+      <c r="S45" s="6" t="inlineStr"/>
       <c r="T45" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U45" s="6" t="inlineStr"/>
+      <c r="U45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="13" t="n">
+      <c r="A46" s="14" t="n">
         <v>44</v>
       </c>
-      <c r="B46" s="14">
+      <c r="B46" s="15">
         <f>A46*1000/60</f>
         <v/>
       </c>
-      <c r="C46" s="13" t="inlineStr">
+      <c r="C46" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D46" s="13" t="inlineStr">
+      <c r="D46" s="14" t="inlineStr">
         <is>
           <t>C14</t>
         </is>
       </c>
-      <c r="E46" s="13" t="inlineStr">
+      <c r="E46" s="14" t="inlineStr">
         <is>
           <t>S2 clip 13</t>
         </is>
       </c>
-      <c r="F46" s="13" t="n">
+      <c r="F46" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G46" s="6" t="n">
@@ -3660,45 +3806,46 @@
       </c>
       <c r="N46" s="6" t="inlineStr"/>
       <c r="O46" s="6" t="inlineStr"/>
-      <c r="P46" s="15" t="inlineStr">
+      <c r="P46" s="16" t="inlineStr">
         <is>
           <t>f2 · 100% · under</t>
         </is>
       </c>
       <c r="Q46" s="6" t="inlineStr"/>
       <c r="R46" s="6" t="inlineStr"/>
-      <c r="S46" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S46" s="6" t="inlineStr"/>
       <c r="T46" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U46" s="6" t="inlineStr"/>
+      <c r="U46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="13" t="n">
+      <c r="A47" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="B47" s="14">
+      <c r="B47" s="15">
         <f>A47*1000/60</f>
         <v/>
       </c>
-      <c r="C47" s="13" t="inlineStr">
+      <c r="C47" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D47" s="13" t="inlineStr">
+      <c r="D47" s="14" t="inlineStr">
         <is>
           <t>C14</t>
         </is>
       </c>
-      <c r="E47" s="13" t="inlineStr">
+      <c r="E47" s="14" t="inlineStr">
         <is>
           <t>S2 clip 13</t>
         </is>
       </c>
-      <c r="F47" s="13" t="n">
+      <c r="F47" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G47" s="6" t="n">
@@ -3725,45 +3872,46 @@
       </c>
       <c r="N47" s="6" t="inlineStr"/>
       <c r="O47" s="6" t="inlineStr"/>
-      <c r="P47" s="15" t="inlineStr">
+      <c r="P47" s="16" t="inlineStr">
         <is>
           <t>f2 · 100% · under</t>
         </is>
       </c>
       <c r="Q47" s="6" t="inlineStr"/>
       <c r="R47" s="6" t="inlineStr"/>
-      <c r="S47" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S47" s="6" t="inlineStr"/>
       <c r="T47" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U47" s="6" t="inlineStr"/>
+      <c r="U47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="13" t="n">
+      <c r="A48" s="14" t="n">
         <v>46</v>
       </c>
-      <c r="B48" s="14">
+      <c r="B48" s="15">
         <f>A48*1000/60</f>
         <v/>
       </c>
-      <c r="C48" s="13" t="inlineStr">
+      <c r="C48" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D48" s="13" t="inlineStr">
+      <c r="D48" s="14" t="inlineStr">
         <is>
           <t>C14</t>
         </is>
       </c>
-      <c r="E48" s="13" t="inlineStr">
+      <c r="E48" s="14" t="inlineStr">
         <is>
           <t>S2 clip 13</t>
         </is>
       </c>
-      <c r="F48" s="13" t="n">
+      <c r="F48" s="14" t="n">
         <v>3</v>
       </c>
       <c r="G48" s="6" t="n">
@@ -3790,45 +3938,46 @@
       </c>
       <c r="N48" s="6" t="inlineStr"/>
       <c r="O48" s="6" t="inlineStr"/>
-      <c r="P48" s="15" t="inlineStr">
+      <c r="P48" s="16" t="inlineStr">
         <is>
           <t>f2 · 100% · under</t>
         </is>
       </c>
       <c r="Q48" s="6" t="inlineStr"/>
       <c r="R48" s="6" t="inlineStr"/>
-      <c r="S48" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S48" s="6" t="inlineStr"/>
       <c r="T48" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U48" s="6" t="inlineStr"/>
+      <c r="U48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="13" t="n">
+      <c r="A49" s="14" t="n">
         <v>47</v>
       </c>
-      <c r="B49" s="14">
+      <c r="B49" s="15">
         <f>A49*1000/60</f>
         <v/>
       </c>
-      <c r="C49" s="13" t="inlineStr">
+      <c r="C49" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D49" s="13" t="inlineStr">
+      <c r="D49" s="14" t="inlineStr">
         <is>
           <t>C14</t>
         </is>
       </c>
-      <c r="E49" s="13" t="inlineStr">
+      <c r="E49" s="14" t="inlineStr">
         <is>
           <t>S2 clip 13</t>
         </is>
       </c>
-      <c r="F49" s="13" t="n">
+      <c r="F49" s="14" t="n">
         <v>4</v>
       </c>
       <c r="G49" s="6" t="n">
@@ -3855,45 +4004,46 @@
       </c>
       <c r="N49" s="6" t="inlineStr"/>
       <c r="O49" s="6" t="inlineStr"/>
-      <c r="P49" s="15" t="inlineStr">
+      <c r="P49" s="16" t="inlineStr">
         <is>
           <t>f2 · 100% · under</t>
         </is>
       </c>
       <c r="Q49" s="6" t="inlineStr"/>
       <c r="R49" s="6" t="inlineStr"/>
-      <c r="S49" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S49" s="6" t="inlineStr"/>
       <c r="T49" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U49" s="6" t="inlineStr"/>
+      <c r="U49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="13" t="n">
+      <c r="A50" s="14" t="n">
         <v>48</v>
       </c>
-      <c r="B50" s="14">
+      <c r="B50" s="15">
         <f>A50*1000/60</f>
         <v/>
       </c>
-      <c r="C50" s="13" t="inlineStr">
+      <c r="C50" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D50" s="13" t="inlineStr">
+      <c r="D50" s="14" t="inlineStr">
         <is>
           <t>C15</t>
         </is>
       </c>
-      <c r="E50" s="13" t="inlineStr">
+      <c r="E50" s="14" t="inlineStr">
         <is>
           <t>S2 clip 14</t>
         </is>
       </c>
-      <c r="F50" s="13" t="n">
+      <c r="F50" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G50" s="6" t="n">
@@ -3920,45 +4070,46 @@
       </c>
       <c r="N50" s="6" t="inlineStr"/>
       <c r="O50" s="6" t="inlineStr"/>
-      <c r="P50" s="15" t="inlineStr">
+      <c r="P50" s="16" t="inlineStr">
         <is>
           <t>f2 · 100% · under</t>
         </is>
       </c>
       <c r="Q50" s="6" t="inlineStr"/>
       <c r="R50" s="6" t="inlineStr"/>
-      <c r="S50" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S50" s="6" t="inlineStr"/>
       <c r="T50" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U50" s="6" t="inlineStr"/>
+      <c r="U50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="13" t="n">
+      <c r="A51" s="14" t="n">
         <v>49</v>
       </c>
-      <c r="B51" s="14">
+      <c r="B51" s="15">
         <f>A51*1000/60</f>
         <v/>
       </c>
-      <c r="C51" s="13" t="inlineStr">
+      <c r="C51" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D51" s="13" t="inlineStr">
+      <c r="D51" s="14" t="inlineStr">
         <is>
           <t>C15</t>
         </is>
       </c>
-      <c r="E51" s="13" t="inlineStr">
+      <c r="E51" s="14" t="inlineStr">
         <is>
           <t>S2 clip 14</t>
         </is>
       </c>
-      <c r="F51" s="13" t="n">
+      <c r="F51" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G51" s="6" t="n">
@@ -3985,45 +4136,46 @@
       </c>
       <c r="N51" s="6" t="inlineStr"/>
       <c r="O51" s="6" t="inlineStr"/>
-      <c r="P51" s="15" t="inlineStr">
+      <c r="P51" s="16" t="inlineStr">
         <is>
           <t>f3 · 100% · under</t>
         </is>
       </c>
       <c r="Q51" s="6" t="inlineStr"/>
       <c r="R51" s="6" t="inlineStr"/>
-      <c r="S51" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S51" s="6" t="inlineStr"/>
       <c r="T51" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U51" s="6" t="inlineStr"/>
+      <c r="U51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="13" t="n">
+      <c r="A52" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="B52" s="14">
+      <c r="B52" s="15">
         <f>A52*1000/60</f>
         <v/>
       </c>
-      <c r="C52" s="13" t="inlineStr">
+      <c r="C52" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D52" s="13" t="inlineStr">
+      <c r="D52" s="14" t="inlineStr">
         <is>
           <t>C15</t>
         </is>
       </c>
-      <c r="E52" s="13" t="inlineStr">
+      <c r="E52" s="14" t="inlineStr">
         <is>
           <t>S2 clip 14</t>
         </is>
       </c>
-      <c r="F52" s="13" t="n">
+      <c r="F52" s="14" t="n">
         <v>3</v>
       </c>
       <c r="G52" s="6" t="n">
@@ -4050,45 +4202,46 @@
       </c>
       <c r="N52" s="6" t="inlineStr"/>
       <c r="O52" s="6" t="inlineStr"/>
-      <c r="P52" s="15" t="inlineStr">
+      <c r="P52" s="16" t="inlineStr">
         <is>
           <t>f3 · 100% · under</t>
         </is>
       </c>
       <c r="Q52" s="6" t="inlineStr"/>
       <c r="R52" s="6" t="inlineStr"/>
-      <c r="S52" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S52" s="6" t="inlineStr"/>
       <c r="T52" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U52" s="6" t="inlineStr"/>
+      <c r="U52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="13" t="n">
+      <c r="A53" s="14" t="n">
         <v>51</v>
       </c>
-      <c r="B53" s="14">
+      <c r="B53" s="15">
         <f>A53*1000/60</f>
         <v/>
       </c>
-      <c r="C53" s="13" t="inlineStr">
+      <c r="C53" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D53" s="13" t="inlineStr">
+      <c r="D53" s="14" t="inlineStr">
         <is>
           <t>C15</t>
         </is>
       </c>
-      <c r="E53" s="13" t="inlineStr">
+      <c r="E53" s="14" t="inlineStr">
         <is>
           <t>S2 clip 14</t>
         </is>
       </c>
-      <c r="F53" s="13" t="n">
+      <c r="F53" s="14" t="n">
         <v>4</v>
       </c>
       <c r="G53" s="6" t="n">
@@ -4115,45 +4268,46 @@
       </c>
       <c r="N53" s="6" t="inlineStr"/>
       <c r="O53" s="6" t="inlineStr"/>
-      <c r="P53" s="15" t="inlineStr">
+      <c r="P53" s="16" t="inlineStr">
         <is>
           <t>f3 · 100% · under</t>
         </is>
       </c>
       <c r="Q53" s="6" t="inlineStr"/>
       <c r="R53" s="6" t="inlineStr"/>
-      <c r="S53" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S53" s="6" t="inlineStr"/>
       <c r="T53" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U53" s="6" t="inlineStr"/>
+      <c r="U53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="13" t="n">
+      <c r="A54" s="14" t="n">
         <v>52</v>
       </c>
-      <c r="B54" s="14">
+      <c r="B54" s="15">
         <f>A54*1000/60</f>
         <v/>
       </c>
-      <c r="C54" s="13" t="inlineStr">
+      <c r="C54" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D54" s="13" t="inlineStr">
+      <c r="D54" s="14" t="inlineStr">
         <is>
           <t>C16</t>
         </is>
       </c>
-      <c r="E54" s="13" t="inlineStr">
+      <c r="E54" s="14" t="inlineStr">
         <is>
           <t>S2 clip 15</t>
         </is>
       </c>
-      <c r="F54" s="13" t="n">
+      <c r="F54" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G54" s="6" t="n">
@@ -4180,45 +4334,46 @@
       </c>
       <c r="N54" s="6" t="inlineStr"/>
       <c r="O54" s="6" t="inlineStr"/>
-      <c r="P54" s="15" t="inlineStr">
+      <c r="P54" s="16" t="inlineStr">
         <is>
           <t>f3 · 100% · under</t>
         </is>
       </c>
       <c r="Q54" s="6" t="inlineStr"/>
       <c r="R54" s="6" t="inlineStr"/>
-      <c r="S54" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S54" s="6" t="inlineStr"/>
       <c r="T54" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U54" s="6" t="inlineStr"/>
+      <c r="U54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="13" t="n">
+      <c r="A55" s="14" t="n">
         <v>53</v>
       </c>
-      <c r="B55" s="14">
+      <c r="B55" s="15">
         <f>A55*1000/60</f>
         <v/>
       </c>
-      <c r="C55" s="13" t="inlineStr">
+      <c r="C55" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D55" s="13" t="inlineStr">
+      <c r="D55" s="14" t="inlineStr">
         <is>
           <t>C16</t>
         </is>
       </c>
-      <c r="E55" s="13" t="inlineStr">
+      <c r="E55" s="14" t="inlineStr">
         <is>
           <t>S2 clip 15</t>
         </is>
       </c>
-      <c r="F55" s="13" t="n">
+      <c r="F55" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G55" s="6" t="n">
@@ -4245,45 +4400,46 @@
       </c>
       <c r="N55" s="6" t="inlineStr"/>
       <c r="O55" s="6" t="inlineStr"/>
-      <c r="P55" s="15" t="inlineStr">
+      <c r="P55" s="16" t="inlineStr">
         <is>
           <t>f4 · 100% · under</t>
         </is>
       </c>
       <c r="Q55" s="6" t="inlineStr"/>
       <c r="R55" s="6" t="inlineStr"/>
-      <c r="S55" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S55" s="6" t="inlineStr"/>
       <c r="T55" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U55" s="6" t="inlineStr"/>
+      <c r="U55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="13" t="n">
+      <c r="A56" s="14" t="n">
         <v>54</v>
       </c>
-      <c r="B56" s="14">
+      <c r="B56" s="15">
         <f>A56*1000/60</f>
         <v/>
       </c>
-      <c r="C56" s="13" t="inlineStr">
+      <c r="C56" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D56" s="13" t="inlineStr">
+      <c r="D56" s="14" t="inlineStr">
         <is>
           <t>C16</t>
         </is>
       </c>
-      <c r="E56" s="13" t="inlineStr">
+      <c r="E56" s="14" t="inlineStr">
         <is>
           <t>S2 clip 15</t>
         </is>
       </c>
-      <c r="F56" s="13" t="n">
+      <c r="F56" s="14" t="n">
         <v>3</v>
       </c>
       <c r="G56" s="6" t="n">
@@ -4310,45 +4466,46 @@
       </c>
       <c r="N56" s="6" t="inlineStr"/>
       <c r="O56" s="6" t="inlineStr"/>
-      <c r="P56" s="15" t="inlineStr">
+      <c r="P56" s="16" t="inlineStr">
         <is>
           <t>f4 · 100% · under</t>
         </is>
       </c>
       <c r="Q56" s="6" t="inlineStr"/>
       <c r="R56" s="6" t="inlineStr"/>
-      <c r="S56" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S56" s="6" t="inlineStr"/>
       <c r="T56" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U56" s="6" t="inlineStr"/>
+      <c r="U56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="13" t="n">
+      <c r="A57" s="14" t="n">
         <v>55</v>
       </c>
-      <c r="B57" s="14">
+      <c r="B57" s="15">
         <f>A57*1000/60</f>
         <v/>
       </c>
-      <c r="C57" s="13" t="inlineStr">
+      <c r="C57" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D57" s="13" t="inlineStr">
+      <c r="D57" s="14" t="inlineStr">
         <is>
           <t>C16</t>
         </is>
       </c>
-      <c r="E57" s="13" t="inlineStr">
+      <c r="E57" s="14" t="inlineStr">
         <is>
           <t>S2 clip 15</t>
         </is>
       </c>
-      <c r="F57" s="13" t="n">
+      <c r="F57" s="14" t="n">
         <v>4</v>
       </c>
       <c r="G57" s="6" t="n">
@@ -4375,45 +4532,46 @@
       </c>
       <c r="N57" s="6" t="inlineStr"/>
       <c r="O57" s="6" t="inlineStr"/>
-      <c r="P57" s="15" t="inlineStr">
+      <c r="P57" s="16" t="inlineStr">
         <is>
           <t>f4 · 100% · under</t>
         </is>
       </c>
       <c r="Q57" s="6" t="inlineStr"/>
       <c r="R57" s="6" t="inlineStr"/>
-      <c r="S57" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S57" s="6" t="inlineStr"/>
       <c r="T57" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U57" s="6" t="inlineStr"/>
+      <c r="U57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="13" t="n">
+      <c r="A58" s="14" t="n">
         <v>56</v>
       </c>
-      <c r="B58" s="14">
+      <c r="B58" s="15">
         <f>A58*1000/60</f>
         <v/>
       </c>
-      <c r="C58" s="13" t="inlineStr">
+      <c r="C58" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D58" s="13" t="inlineStr">
+      <c r="D58" s="14" t="inlineStr">
         <is>
           <t>C17</t>
         </is>
       </c>
-      <c r="E58" s="13" t="inlineStr">
+      <c r="E58" s="14" t="inlineStr">
         <is>
           <t>S2 clip 16</t>
         </is>
       </c>
-      <c r="F58" s="13" t="n">
+      <c r="F58" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G58" s="6" t="n">
@@ -4440,45 +4598,46 @@
       </c>
       <c r="N58" s="6" t="inlineStr"/>
       <c r="O58" s="6" t="inlineStr"/>
-      <c r="P58" s="15" t="inlineStr">
+      <c r="P58" s="16" t="inlineStr">
         <is>
           <t>f4 · 100% · under</t>
         </is>
       </c>
       <c r="Q58" s="6" t="inlineStr"/>
       <c r="R58" s="6" t="inlineStr"/>
-      <c r="S58" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S58" s="6" t="inlineStr"/>
       <c r="T58" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U58" s="6" t="inlineStr"/>
+      <c r="U58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="13" t="n">
+      <c r="A59" s="14" t="n">
         <v>57</v>
       </c>
-      <c r="B59" s="14">
+      <c r="B59" s="15">
         <f>A59*1000/60</f>
         <v/>
       </c>
-      <c r="C59" s="13" t="inlineStr">
+      <c r="C59" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D59" s="13" t="inlineStr">
+      <c r="D59" s="14" t="inlineStr">
         <is>
           <t>C17</t>
         </is>
       </c>
-      <c r="E59" s="13" t="inlineStr">
+      <c r="E59" s="14" t="inlineStr">
         <is>
           <t>S2 clip 16</t>
         </is>
       </c>
-      <c r="F59" s="13" t="n">
+      <c r="F59" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G59" s="6" t="n">
@@ -4505,45 +4664,46 @@
       </c>
       <c r="N59" s="6" t="inlineStr"/>
       <c r="O59" s="6" t="inlineStr"/>
-      <c r="P59" s="15" t="inlineStr">
+      <c r="P59" s="16" t="inlineStr">
         <is>
           <t>f4 · 100% · under</t>
         </is>
       </c>
       <c r="Q59" s="6" t="inlineStr"/>
       <c r="R59" s="6" t="inlineStr"/>
-      <c r="S59" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S59" s="6" t="inlineStr"/>
       <c r="T59" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U59" s="6" t="inlineStr"/>
+      <c r="U59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="13" t="n">
+      <c r="A60" s="14" t="n">
         <v>58</v>
       </c>
-      <c r="B60" s="14">
+      <c r="B60" s="15">
         <f>A60*1000/60</f>
         <v/>
       </c>
-      <c r="C60" s="13" t="inlineStr">
+      <c r="C60" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D60" s="13" t="inlineStr">
+      <c r="D60" s="14" t="inlineStr">
         <is>
           <t>C17</t>
         </is>
       </c>
-      <c r="E60" s="13" t="inlineStr">
+      <c r="E60" s="14" t="inlineStr">
         <is>
           <t>S2 clip 16</t>
         </is>
       </c>
-      <c r="F60" s="13" t="n">
+      <c r="F60" s="14" t="n">
         <v>3</v>
       </c>
       <c r="G60" s="6" t="n">
@@ -4570,45 +4730,46 @@
       </c>
       <c r="N60" s="6" t="inlineStr"/>
       <c r="O60" s="6" t="inlineStr"/>
-      <c r="P60" s="15" t="inlineStr">
+      <c r="P60" s="16" t="inlineStr">
         <is>
           <t>f5 · 100% · under</t>
         </is>
       </c>
       <c r="Q60" s="6" t="inlineStr"/>
       <c r="R60" s="6" t="inlineStr"/>
-      <c r="S60" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S60" s="6" t="inlineStr"/>
       <c r="T60" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U60" s="6" t="inlineStr"/>
+      <c r="U60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="13" t="n">
+      <c r="A61" s="14" t="n">
         <v>59</v>
       </c>
-      <c r="B61" s="14">
+      <c r="B61" s="15">
         <f>A61*1000/60</f>
         <v/>
       </c>
-      <c r="C61" s="13" t="inlineStr">
+      <c r="C61" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D61" s="13" t="inlineStr">
+      <c r="D61" s="14" t="inlineStr">
         <is>
           <t>C17</t>
         </is>
       </c>
-      <c r="E61" s="13" t="inlineStr">
+      <c r="E61" s="14" t="inlineStr">
         <is>
           <t>S2 clip 16</t>
         </is>
       </c>
-      <c r="F61" s="13" t="n">
+      <c r="F61" s="14" t="n">
         <v>4</v>
       </c>
       <c r="G61" s="6" t="n">
@@ -4635,45 +4796,46 @@
       </c>
       <c r="N61" s="6" t="inlineStr"/>
       <c r="O61" s="6" t="inlineStr"/>
-      <c r="P61" s="15" t="inlineStr">
+      <c r="P61" s="16" t="inlineStr">
         <is>
           <t>f5 · 100% · under</t>
         </is>
       </c>
       <c r="Q61" s="6" t="inlineStr"/>
       <c r="R61" s="6" t="inlineStr"/>
-      <c r="S61" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S61" s="6" t="inlineStr"/>
       <c r="T61" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U61" s="6" t="inlineStr"/>
+      <c r="U61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="13" t="n">
+      <c r="A62" s="14" t="n">
         <v>60</v>
       </c>
-      <c r="B62" s="14">
+      <c r="B62" s="15">
         <f>A62*1000/60</f>
         <v/>
       </c>
-      <c r="C62" s="13" t="inlineStr">
+      <c r="C62" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D62" s="13" t="inlineStr">
+      <c r="D62" s="14" t="inlineStr">
         <is>
           <t>C18</t>
         </is>
       </c>
-      <c r="E62" s="13" t="inlineStr">
+      <c r="E62" s="14" t="inlineStr">
         <is>
           <t>S2 clip 17</t>
         </is>
       </c>
-      <c r="F62" s="13" t="n">
+      <c r="F62" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G62" s="6" t="n">
@@ -4700,45 +4862,46 @@
       </c>
       <c r="N62" s="6" t="inlineStr"/>
       <c r="O62" s="6" t="inlineStr"/>
-      <c r="P62" s="15" t="inlineStr">
+      <c r="P62" s="16" t="inlineStr">
         <is>
           <t>f5 · 100% · under</t>
         </is>
       </c>
       <c r="Q62" s="6" t="inlineStr"/>
       <c r="R62" s="6" t="inlineStr"/>
-      <c r="S62" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S62" s="6" t="inlineStr"/>
       <c r="T62" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U62" s="6" t="inlineStr"/>
+      <c r="U62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="13" t="n">
+      <c r="A63" s="14" t="n">
         <v>61</v>
       </c>
-      <c r="B63" s="14">
+      <c r="B63" s="15">
         <f>A63*1000/60</f>
         <v/>
       </c>
-      <c r="C63" s="13" t="inlineStr">
+      <c r="C63" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D63" s="13" t="inlineStr">
+      <c r="D63" s="14" t="inlineStr">
         <is>
           <t>C18</t>
         </is>
       </c>
-      <c r="E63" s="13" t="inlineStr">
+      <c r="E63" s="14" t="inlineStr">
         <is>
           <t>S2 clip 17</t>
         </is>
       </c>
-      <c r="F63" s="13" t="n">
+      <c r="F63" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G63" s="6" t="n">
@@ -4765,45 +4928,46 @@
       </c>
       <c r="N63" s="6" t="inlineStr"/>
       <c r="O63" s="6" t="inlineStr"/>
-      <c r="P63" s="15" t="inlineStr">
+      <c r="P63" s="16" t="inlineStr">
         <is>
           <t>f5 · 100% · under</t>
         </is>
       </c>
       <c r="Q63" s="6" t="inlineStr"/>
       <c r="R63" s="6" t="inlineStr"/>
-      <c r="S63" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S63" s="6" t="inlineStr"/>
       <c r="T63" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U63" s="6" t="inlineStr"/>
+      <c r="U63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="13" t="n">
+      <c r="A64" s="14" t="n">
         <v>62</v>
       </c>
-      <c r="B64" s="14">
+      <c r="B64" s="15">
         <f>A64*1000/60</f>
         <v/>
       </c>
-      <c r="C64" s="13" t="inlineStr">
+      <c r="C64" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D64" s="13" t="inlineStr">
+      <c r="D64" s="14" t="inlineStr">
         <is>
           <t>C18</t>
         </is>
       </c>
-      <c r="E64" s="13" t="inlineStr">
+      <c r="E64" s="14" t="inlineStr">
         <is>
           <t>S2 clip 17</t>
         </is>
       </c>
-      <c r="F64" s="13" t="n">
+      <c r="F64" s="14" t="n">
         <v>3</v>
       </c>
       <c r="G64" s="6" t="n">
@@ -4830,45 +4994,46 @@
       </c>
       <c r="N64" s="6" t="inlineStr"/>
       <c r="O64" s="6" t="inlineStr"/>
-      <c r="P64" s="15" t="inlineStr">
+      <c r="P64" s="16" t="inlineStr">
         <is>
           <t>f5 · 100% · under</t>
         </is>
       </c>
       <c r="Q64" s="6" t="inlineStr"/>
       <c r="R64" s="6" t="inlineStr"/>
-      <c r="S64" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S64" s="6" t="inlineStr"/>
       <c r="T64" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U64" s="6" t="inlineStr"/>
+      <c r="U64" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" s="6" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="13" t="n">
+      <c r="A65" s="14" t="n">
         <v>63</v>
       </c>
-      <c r="B65" s="14">
+      <c r="B65" s="15">
         <f>A65*1000/60</f>
         <v/>
       </c>
-      <c r="C65" s="13" t="inlineStr">
+      <c r="C65" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D65" s="13" t="inlineStr">
+      <c r="D65" s="14" t="inlineStr">
         <is>
           <t>C18</t>
         </is>
       </c>
-      <c r="E65" s="13" t="inlineStr">
+      <c r="E65" s="14" t="inlineStr">
         <is>
           <t>S2 clip 17</t>
         </is>
       </c>
-      <c r="F65" s="13" t="n">
+      <c r="F65" s="14" t="n">
         <v>4</v>
       </c>
       <c r="G65" s="6" t="n">
@@ -4895,45 +5060,46 @@
       </c>
       <c r="N65" s="6" t="inlineStr"/>
       <c r="O65" s="6" t="inlineStr"/>
-      <c r="P65" s="15" t="inlineStr">
+      <c r="P65" s="16" t="inlineStr">
         <is>
           <t>f6 · 100% · under</t>
         </is>
       </c>
       <c r="Q65" s="6" t="inlineStr"/>
       <c r="R65" s="6" t="inlineStr"/>
-      <c r="S65" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S65" s="6" t="inlineStr"/>
       <c r="T65" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U65" s="6" t="inlineStr"/>
+      <c r="U65" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="13" t="n">
+      <c r="A66" s="14" t="n">
         <v>64</v>
       </c>
-      <c r="B66" s="14">
+      <c r="B66" s="15">
         <f>A66*1000/60</f>
         <v/>
       </c>
-      <c r="C66" s="13" t="inlineStr">
+      <c r="C66" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D66" s="13" t="inlineStr">
+      <c r="D66" s="14" t="inlineStr">
         <is>
           <t>C18</t>
         </is>
       </c>
-      <c r="E66" s="13" t="inlineStr">
+      <c r="E66" s="14" t="inlineStr">
         <is>
           <t>S2 clip 17</t>
         </is>
       </c>
-      <c r="F66" s="13" t="n">
+      <c r="F66" s="14" t="n">
         <v>5</v>
       </c>
       <c r="G66" s="6" t="n">
@@ -4960,45 +5126,46 @@
       </c>
       <c r="N66" s="6" t="inlineStr"/>
       <c r="O66" s="6" t="inlineStr"/>
-      <c r="P66" s="15" t="inlineStr">
+      <c r="P66" s="16" t="inlineStr">
         <is>
           <t>f6 · 100% · under</t>
         </is>
       </c>
       <c r="Q66" s="6" t="inlineStr"/>
       <c r="R66" s="6" t="inlineStr"/>
-      <c r="S66" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S66" s="6" t="inlineStr"/>
       <c r="T66" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U66" s="6" t="inlineStr"/>
+      <c r="U66" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="13" t="n">
+      <c r="A67" s="14" t="n">
         <v>65</v>
       </c>
-      <c r="B67" s="14">
+      <c r="B67" s="15">
         <f>A67*1000/60</f>
         <v/>
       </c>
-      <c r="C67" s="13" t="inlineStr">
+      <c r="C67" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D67" s="13" t="inlineStr">
+      <c r="D67" s="14" t="inlineStr">
         <is>
           <t>C19</t>
         </is>
       </c>
-      <c r="E67" s="13" t="inlineStr">
+      <c r="E67" s="14" t="inlineStr">
         <is>
           <t>S2 clip 18</t>
         </is>
       </c>
-      <c r="F67" s="13" t="n">
+      <c r="F67" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G67" s="6" t="n">
@@ -5025,45 +5192,46 @@
       </c>
       <c r="N67" s="6" t="inlineStr"/>
       <c r="O67" s="6" t="inlineStr"/>
-      <c r="P67" s="15" t="inlineStr">
+      <c r="P67" s="16" t="inlineStr">
         <is>
           <t>f6 · 100% · under</t>
         </is>
       </c>
       <c r="Q67" s="6" t="inlineStr"/>
       <c r="R67" s="6" t="inlineStr"/>
-      <c r="S67" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S67" s="6" t="inlineStr"/>
       <c r="T67" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U67" s="6" t="inlineStr"/>
+      <c r="U67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" s="6" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="13" t="n">
+      <c r="A68" s="14" t="n">
         <v>66</v>
       </c>
-      <c r="B68" s="14">
+      <c r="B68" s="15">
         <f>A68*1000/60</f>
         <v/>
       </c>
-      <c r="C68" s="13" t="inlineStr">
+      <c r="C68" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D68" s="13" t="inlineStr">
+      <c r="D68" s="14" t="inlineStr">
         <is>
           <t>C19</t>
         </is>
       </c>
-      <c r="E68" s="13" t="inlineStr">
+      <c r="E68" s="14" t="inlineStr">
         <is>
           <t>S2 clip 18</t>
         </is>
       </c>
-      <c r="F68" s="13" t="n">
+      <c r="F68" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G68" s="6" t="n">
@@ -5090,45 +5258,46 @@
       </c>
       <c r="N68" s="6" t="inlineStr"/>
       <c r="O68" s="6" t="inlineStr"/>
-      <c r="P68" s="15" t="inlineStr">
+      <c r="P68" s="16" t="inlineStr">
         <is>
           <t>f6 · 100% · under</t>
         </is>
       </c>
       <c r="Q68" s="6" t="inlineStr"/>
       <c r="R68" s="6" t="inlineStr"/>
-      <c r="S68" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S68" s="6" t="inlineStr"/>
       <c r="T68" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U68" s="6" t="inlineStr"/>
+      <c r="U68" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" s="6" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="13" t="n">
+      <c r="A69" s="14" t="n">
         <v>67</v>
       </c>
-      <c r="B69" s="14">
+      <c r="B69" s="15">
         <f>A69*1000/60</f>
         <v/>
       </c>
-      <c r="C69" s="13" t="inlineStr">
+      <c r="C69" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D69" s="13" t="inlineStr">
+      <c r="D69" s="14" t="inlineStr">
         <is>
           <t>C19</t>
         </is>
       </c>
-      <c r="E69" s="13" t="inlineStr">
+      <c r="E69" s="14" t="inlineStr">
         <is>
           <t>S2 clip 18</t>
         </is>
       </c>
-      <c r="F69" s="13" t="n">
+      <c r="F69" s="14" t="n">
         <v>3</v>
       </c>
       <c r="G69" s="6" t="n">
@@ -5155,45 +5324,46 @@
       </c>
       <c r="N69" s="6" t="inlineStr"/>
       <c r="O69" s="6" t="inlineStr"/>
-      <c r="P69" s="15" t="inlineStr">
+      <c r="P69" s="16" t="inlineStr">
         <is>
           <t>f7 · 100% · under</t>
         </is>
       </c>
       <c r="Q69" s="6" t="inlineStr"/>
       <c r="R69" s="6" t="inlineStr"/>
-      <c r="S69" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S69" s="6" t="inlineStr"/>
       <c r="T69" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U69" s="6" t="inlineStr"/>
+      <c r="U69" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" s="6" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="13" t="n">
+      <c r="A70" s="14" t="n">
         <v>68</v>
       </c>
-      <c r="B70" s="14">
+      <c r="B70" s="15">
         <f>A70*1000/60</f>
         <v/>
       </c>
-      <c r="C70" s="13" t="inlineStr">
+      <c r="C70" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D70" s="13" t="inlineStr">
+      <c r="D70" s="14" t="inlineStr">
         <is>
           <t>C20</t>
         </is>
       </c>
-      <c r="E70" s="13" t="inlineStr">
+      <c r="E70" s="14" t="inlineStr">
         <is>
           <t>S2 clip 19</t>
         </is>
       </c>
-      <c r="F70" s="13" t="n">
+      <c r="F70" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G70" s="6" t="n">
@@ -5220,45 +5390,46 @@
       </c>
       <c r="N70" s="6" t="inlineStr"/>
       <c r="O70" s="6" t="inlineStr"/>
-      <c r="P70" s="15" t="inlineStr">
+      <c r="P70" s="16" t="inlineStr">
         <is>
           <t>f7 · 100% · under</t>
         </is>
       </c>
       <c r="Q70" s="6" t="inlineStr"/>
       <c r="R70" s="6" t="inlineStr"/>
-      <c r="S70" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S70" s="6" t="inlineStr"/>
       <c r="T70" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U70" s="6" t="inlineStr"/>
+      <c r="U70" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" s="6" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="13" t="n">
+      <c r="A71" s="14" t="n">
         <v>69</v>
       </c>
-      <c r="B71" s="14">
+      <c r="B71" s="15">
         <f>A71*1000/60</f>
         <v/>
       </c>
-      <c r="C71" s="13" t="inlineStr">
+      <c r="C71" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D71" s="13" t="inlineStr">
+      <c r="D71" s="14" t="inlineStr">
         <is>
           <t>C20</t>
         </is>
       </c>
-      <c r="E71" s="13" t="inlineStr">
+      <c r="E71" s="14" t="inlineStr">
         <is>
           <t>S2 clip 19</t>
         </is>
       </c>
-      <c r="F71" s="13" t="n">
+      <c r="F71" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G71" s="6" t="n">
@@ -5285,45 +5456,46 @@
       </c>
       <c r="N71" s="6" t="inlineStr"/>
       <c r="O71" s="6" t="inlineStr"/>
-      <c r="P71" s="15" t="inlineStr">
+      <c r="P71" s="16" t="inlineStr">
         <is>
           <t>f7 · 100% · under</t>
         </is>
       </c>
       <c r="Q71" s="6" t="inlineStr"/>
       <c r="R71" s="6" t="inlineStr"/>
-      <c r="S71" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S71" s="6" t="inlineStr"/>
       <c r="T71" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U71" s="6" t="inlineStr"/>
+      <c r="U71" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" s="6" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="13" t="n">
+      <c r="A72" s="14" t="n">
         <v>70</v>
       </c>
-      <c r="B72" s="14">
+      <c r="B72" s="15">
         <f>A72*1000/60</f>
         <v/>
       </c>
-      <c r="C72" s="13" t="inlineStr">
+      <c r="C72" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D72" s="13" t="inlineStr">
+      <c r="D72" s="14" t="inlineStr">
         <is>
           <t>C20</t>
         </is>
       </c>
-      <c r="E72" s="13" t="inlineStr">
+      <c r="E72" s="14" t="inlineStr">
         <is>
           <t>S2 clip 19</t>
         </is>
       </c>
-      <c r="F72" s="13" t="n">
+      <c r="F72" s="14" t="n">
         <v>3</v>
       </c>
       <c r="G72" s="6" t="n">
@@ -5350,45 +5522,46 @@
       </c>
       <c r="N72" s="6" t="inlineStr"/>
       <c r="O72" s="6" t="inlineStr"/>
-      <c r="P72" s="15" t="inlineStr">
+      <c r="P72" s="16" t="inlineStr">
         <is>
           <t>f7 · 100% · under</t>
         </is>
       </c>
       <c r="Q72" s="6" t="inlineStr"/>
       <c r="R72" s="6" t="inlineStr"/>
-      <c r="S72" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S72" s="6" t="inlineStr"/>
       <c r="T72" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U72" s="6" t="inlineStr"/>
+      <c r="U72" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" s="6" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="13" t="n">
+      <c r="A73" s="14" t="n">
         <v>71</v>
       </c>
-      <c r="B73" s="14">
+      <c r="B73" s="15">
         <f>A73*1000/60</f>
         <v/>
       </c>
-      <c r="C73" s="13" t="inlineStr">
+      <c r="C73" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D73" s="13" t="inlineStr">
+      <c r="D73" s="14" t="inlineStr">
         <is>
           <t>C21</t>
         </is>
       </c>
-      <c r="E73" s="13" t="inlineStr">
+      <c r="E73" s="14" t="inlineStr">
         <is>
           <t>S2 clip 20</t>
         </is>
       </c>
-      <c r="F73" s="13" t="n">
+      <c r="F73" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G73" s="6" t="n">
@@ -5415,45 +5588,46 @@
       </c>
       <c r="N73" s="6" t="inlineStr"/>
       <c r="O73" s="6" t="inlineStr"/>
-      <c r="P73" s="15" t="inlineStr">
+      <c r="P73" s="16" t="inlineStr">
         <is>
           <t>f7 · 100% · under</t>
         </is>
       </c>
       <c r="Q73" s="6" t="inlineStr"/>
       <c r="R73" s="6" t="inlineStr"/>
-      <c r="S73" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S73" s="6" t="inlineStr"/>
       <c r="T73" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U73" s="6" t="inlineStr"/>
+      <c r="U73" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" s="6" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="13" t="n">
+      <c r="A74" s="14" t="n">
         <v>72</v>
       </c>
-      <c r="B74" s="14">
+      <c r="B74" s="15">
         <f>A74*1000/60</f>
         <v/>
       </c>
-      <c r="C74" s="13" t="inlineStr">
+      <c r="C74" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D74" s="13" t="inlineStr">
+      <c r="D74" s="14" t="inlineStr">
         <is>
           <t>C21</t>
         </is>
       </c>
-      <c r="E74" s="13" t="inlineStr">
+      <c r="E74" s="14" t="inlineStr">
         <is>
           <t>S2 clip 20</t>
         </is>
       </c>
-      <c r="F74" s="13" t="n">
+      <c r="F74" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G74" s="6" t="n">
@@ -5480,45 +5654,46 @@
       </c>
       <c r="N74" s="6" t="inlineStr"/>
       <c r="O74" s="6" t="inlineStr"/>
-      <c r="P74" s="15" t="inlineStr">
+      <c r="P74" s="16" t="inlineStr">
         <is>
           <t>f8 · 100% · under</t>
         </is>
       </c>
       <c r="Q74" s="6" t="inlineStr"/>
       <c r="R74" s="6" t="inlineStr"/>
-      <c r="S74" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S74" s="6" t="inlineStr"/>
       <c r="T74" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U74" s="6" t="inlineStr"/>
+      <c r="U74" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" s="6" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="13" t="n">
+      <c r="A75" s="14" t="n">
         <v>73</v>
       </c>
-      <c r="B75" s="14">
+      <c r="B75" s="15">
         <f>A75*1000/60</f>
         <v/>
       </c>
-      <c r="C75" s="13" t="inlineStr">
+      <c r="C75" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D75" s="13" t="inlineStr">
+      <c r="D75" s="14" t="inlineStr">
         <is>
           <t>C21</t>
         </is>
       </c>
-      <c r="E75" s="13" t="inlineStr">
+      <c r="E75" s="14" t="inlineStr">
         <is>
           <t>S2 clip 20</t>
         </is>
       </c>
-      <c r="F75" s="13" t="n">
+      <c r="F75" s="14" t="n">
         <v>3</v>
       </c>
       <c r="G75" s="6" t="n">
@@ -5549,49 +5724,50 @@
         </is>
       </c>
       <c r="O75" s="6" t="inlineStr"/>
-      <c r="P75" s="15" t="inlineStr">
+      <c r="P75" s="16" t="inlineStr">
         <is>
           <t>f8 · 100% · under</t>
         </is>
       </c>
       <c r="Q75" s="6" t="inlineStr"/>
       <c r="R75" s="6" t="inlineStr"/>
-      <c r="S75" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S75" s="6" t="inlineStr"/>
       <c r="T75" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U75" s="6" t="inlineStr">
+      <c r="U75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" s="6" t="inlineStr">
         <is>
           <t>C22</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="13" t="n">
+      <c r="A76" s="14" t="n">
         <v>74</v>
       </c>
-      <c r="B76" s="14">
+      <c r="B76" s="15">
         <f>A76*1000/60</f>
         <v/>
       </c>
-      <c r="C76" s="13" t="inlineStr">
+      <c r="C76" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D76" s="13" t="inlineStr">
+      <c r="D76" s="14" t="inlineStr">
         <is>
           <t>C22</t>
         </is>
       </c>
-      <c r="E76" s="13" t="inlineStr">
+      <c r="E76" s="14" t="inlineStr">
         <is>
           <t>S2 clip 21</t>
         </is>
       </c>
-      <c r="F76" s="13" t="n">
+      <c r="F76" s="14" t="n">
         <v>1</v>
       </c>
       <c r="G76" s="6" t="n">
@@ -5618,45 +5794,46 @@
       </c>
       <c r="N76" s="6" t="inlineStr"/>
       <c r="O76" s="6" t="inlineStr"/>
-      <c r="P76" s="15" t="inlineStr">
+      <c r="P76" s="16" t="inlineStr">
         <is>
           <t>f8 · 100% · under</t>
         </is>
       </c>
       <c r="Q76" s="6" t="inlineStr"/>
       <c r="R76" s="6" t="inlineStr"/>
-      <c r="S76" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S76" s="6" t="inlineStr"/>
       <c r="T76" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U76" s="6" t="inlineStr"/>
+      <c r="U76" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" s="6" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="13" t="n">
+      <c r="A77" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="B77" s="14">
+      <c r="B77" s="15">
         <f>A77*1000/60</f>
         <v/>
       </c>
-      <c r="C77" s="13" t="inlineStr">
+      <c r="C77" s="14" t="inlineStr">
         <is>
           <t>D ควงไม้ = ชาร์จวง (ไม่มีดาเมจ)</t>
         </is>
       </c>
-      <c r="D77" s="13" t="inlineStr">
+      <c r="D77" s="14" t="inlineStr">
         <is>
           <t>C22</t>
         </is>
       </c>
-      <c r="E77" s="13" t="inlineStr">
+      <c r="E77" s="14" t="inlineStr">
         <is>
           <t>S2 clip 21</t>
         </is>
       </c>
-      <c r="F77" s="13" t="n">
+      <c r="F77" s="14" t="n">
         <v>2</v>
       </c>
       <c r="G77" s="6" t="n">
@@ -5683,45 +5860,46 @@
       </c>
       <c r="N77" s="6" t="inlineStr"/>
       <c r="O77" s="6" t="inlineStr"/>
-      <c r="P77" s="15" t="inlineStr">
+      <c r="P77" s="16" t="inlineStr">
         <is>
           <t>f8 · 100% · under</t>
         </is>
       </c>
       <c r="Q77" s="6" t="inlineStr"/>
       <c r="R77" s="6" t="inlineStr"/>
-      <c r="S77" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S77" s="6" t="inlineStr"/>
       <c r="T77" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U77" s="6" t="inlineStr"/>
+      <c r="U77" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" s="6" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="16" t="n">
+      <c r="A78" s="17" t="n">
         <v>76</v>
       </c>
-      <c r="B78" s="17">
+      <c r="B78" s="18">
         <f>A78*1000/60</f>
         <v/>
       </c>
-      <c r="C78" s="16" t="inlineStr">
+      <c r="C78" s="17" t="inlineStr">
         <is>
           <t>E ระเบิดวง + ดาเมจ/ดีบัฟ</t>
         </is>
       </c>
-      <c r="D78" s="16" t="inlineStr">
+      <c r="D78" s="17" t="inlineStr">
         <is>
           <t>C22</t>
         </is>
       </c>
-      <c r="E78" s="16" t="inlineStr">
+      <c r="E78" s="17" t="inlineStr">
         <is>
           <t>S2 clip 21</t>
         </is>
       </c>
-      <c r="F78" s="16" t="n">
+      <c r="F78" s="17" t="n">
         <v>3</v>
       </c>
       <c r="G78" s="6" t="n">
@@ -5752,49 +5930,50 @@
         </is>
       </c>
       <c r="O78" s="6" t="inlineStr"/>
-      <c r="P78" s="15" t="inlineStr">
+      <c r="P78" s="16" t="inlineStr">
         <is>
           <t>f8 · 100% · under</t>
         </is>
       </c>
       <c r="Q78" s="6" t="inlineStr"/>
       <c r="R78" s="6" t="inlineStr"/>
-      <c r="S78" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S78" s="6" t="inlineStr"/>
       <c r="T78" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U78" s="6" t="inlineStr">
+      <c r="U78" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" s="6" t="inlineStr">
         <is>
           <t>C23 · loop หยุดทันที · burst เกิด</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="16" t="n">
+      <c r="A79" s="17" t="n">
         <v>77</v>
       </c>
-      <c r="B79" s="17">
+      <c r="B79" s="18">
         <f>A79*1000/60</f>
         <v/>
       </c>
-      <c r="C79" s="16" t="inlineStr">
+      <c r="C79" s="17" t="inlineStr">
         <is>
           <t>E ระเบิดวง + ดาเมจ/ดีบัฟ</t>
         </is>
       </c>
-      <c r="D79" s="16" t="inlineStr">
+      <c r="D79" s="17" t="inlineStr">
         <is>
           <t>C23</t>
         </is>
       </c>
-      <c r="E79" s="16" t="inlineStr">
+      <c r="E79" s="17" t="inlineStr">
         <is>
           <t>S2 clip 22</t>
         </is>
       </c>
-      <c r="F79" s="16" t="n">
+      <c r="F79" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G79" s="6" t="n">
@@ -5822,44 +6001,49 @@
       <c r="N79" s="6" t="inlineStr"/>
       <c r="O79" s="6" t="inlineStr"/>
       <c r="P79" s="6" t="inlineStr"/>
-      <c r="Q79" s="18" t="inlineStr">
+      <c r="Q79" s="19" t="inlineStr">
+        <is>
+          <t>f1 · 100% · under</t>
+        </is>
+      </c>
+      <c r="R79" s="13" t="inlineStr">
         <is>
           <t>f1 · 100% · over</t>
         </is>
       </c>
-      <c r="R79" s="6" t="inlineStr"/>
-      <c r="S79" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S79" s="6" t="inlineStr"/>
       <c r="T79" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U79" s="6" t="inlineStr"/>
+      <c r="U79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" s="6" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="16" t="n">
+      <c r="A80" s="17" t="n">
         <v>78</v>
       </c>
-      <c r="B80" s="17">
+      <c r="B80" s="18">
         <f>A80*1000/60</f>
         <v/>
       </c>
-      <c r="C80" s="16" t="inlineStr">
+      <c r="C80" s="17" t="inlineStr">
         <is>
           <t>E ระเบิดวง + ดาเมจ/ดีบัฟ</t>
         </is>
       </c>
-      <c r="D80" s="16" t="inlineStr">
+      <c r="D80" s="17" t="inlineStr">
         <is>
           <t>C23</t>
         </is>
       </c>
-      <c r="E80" s="16" t="inlineStr">
+      <c r="E80" s="17" t="inlineStr">
         <is>
           <t>S2 clip 22</t>
         </is>
       </c>
-      <c r="F80" s="16" t="n">
+      <c r="F80" s="17" t="n">
         <v>2</v>
       </c>
       <c r="G80" s="6" t="n">
@@ -5887,44 +6071,49 @@
       <c r="N80" s="6" t="inlineStr"/>
       <c r="O80" s="6" t="inlineStr"/>
       <c r="P80" s="6" t="inlineStr"/>
-      <c r="Q80" s="18" t="inlineStr">
+      <c r="Q80" s="19" t="inlineStr">
+        <is>
+          <t>f1 · 100% · under</t>
+        </is>
+      </c>
+      <c r="R80" s="13" t="inlineStr">
         <is>
           <t>f1 · 100% · over</t>
         </is>
       </c>
-      <c r="R80" s="6" t="inlineStr"/>
-      <c r="S80" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S80" s="6" t="inlineStr"/>
       <c r="T80" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U80" s="6" t="inlineStr"/>
+      <c r="U80" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" s="6" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="16" t="n">
+      <c r="A81" s="17" t="n">
         <v>79</v>
       </c>
-      <c r="B81" s="17">
+      <c r="B81" s="18">
         <f>A81*1000/60</f>
         <v/>
       </c>
-      <c r="C81" s="16" t="inlineStr">
+      <c r="C81" s="17" t="inlineStr">
         <is>
           <t>E ระเบิดวง + ดาเมจ/ดีบัฟ</t>
         </is>
       </c>
-      <c r="D81" s="16" t="inlineStr">
+      <c r="D81" s="17" t="inlineStr">
         <is>
           <t>C23</t>
         </is>
       </c>
-      <c r="E81" s="16" t="inlineStr">
+      <c r="E81" s="17" t="inlineStr">
         <is>
           <t>S2 clip 22</t>
         </is>
       </c>
-      <c r="F81" s="16" t="n">
+      <c r="F81" s="17" t="n">
         <v>3</v>
       </c>
       <c r="G81" s="6" t="n">
@@ -5952,44 +6141,49 @@
       <c r="N81" s="6" t="inlineStr"/>
       <c r="O81" s="6" t="inlineStr"/>
       <c r="P81" s="6" t="inlineStr"/>
-      <c r="Q81" s="18" t="inlineStr">
-        <is>
-          <t>f1 · 100% · over</t>
-        </is>
-      </c>
-      <c r="R81" s="6" t="inlineStr"/>
-      <c r="S81" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q81" s="19" t="inlineStr">
+        <is>
+          <t>f1 · 100% · under</t>
+        </is>
+      </c>
+      <c r="R81" s="13" t="inlineStr">
+        <is>
+          <t>f2 · 100% · over</t>
+        </is>
+      </c>
+      <c r="S81" s="6" t="inlineStr"/>
       <c r="T81" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U81" s="6" t="inlineStr"/>
+      <c r="U81" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" s="6" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="16" t="n">
+      <c r="A82" s="17" t="n">
         <v>80</v>
       </c>
-      <c r="B82" s="17">
+      <c r="B82" s="18">
         <f>A82*1000/60</f>
         <v/>
       </c>
-      <c r="C82" s="16" t="inlineStr">
+      <c r="C82" s="17" t="inlineStr">
         <is>
           <t>E ระเบิดวง + ดาเมจ/ดีบัฟ</t>
         </is>
       </c>
-      <c r="D82" s="16" t="inlineStr">
+      <c r="D82" s="17" t="inlineStr">
         <is>
           <t>C23</t>
         </is>
       </c>
-      <c r="E82" s="16" t="inlineStr">
+      <c r="E82" s="17" t="inlineStr">
         <is>
           <t>S2 clip 22</t>
         </is>
       </c>
-      <c r="F82" s="16" t="n">
+      <c r="F82" s="17" t="n">
         <v>4</v>
       </c>
       <c r="G82" s="6" t="n">
@@ -6017,44 +6211,49 @@
       <c r="N82" s="6" t="inlineStr"/>
       <c r="O82" s="6" t="inlineStr"/>
       <c r="P82" s="6" t="inlineStr"/>
-      <c r="Q82" s="18" t="inlineStr">
+      <c r="Q82" s="19" t="inlineStr">
+        <is>
+          <t>f2 · 100% · under</t>
+        </is>
+      </c>
+      <c r="R82" s="13" t="inlineStr">
         <is>
           <t>f2 · 100% · over</t>
         </is>
       </c>
-      <c r="R82" s="6" t="inlineStr"/>
-      <c r="S82" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S82" s="6" t="inlineStr"/>
       <c r="T82" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U82" s="6" t="inlineStr"/>
+      <c r="U82" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" s="6" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="16" t="n">
+      <c r="A83" s="17" t="n">
         <v>81</v>
       </c>
-      <c r="B83" s="17">
+      <c r="B83" s="18">
         <f>A83*1000/60</f>
         <v/>
       </c>
-      <c r="C83" s="16" t="inlineStr">
+      <c r="C83" s="17" t="inlineStr">
         <is>
           <t>E ระเบิดวง + ดาเมจ/ดีบัฟ</t>
         </is>
       </c>
-      <c r="D83" s="16" t="inlineStr">
+      <c r="D83" s="17" t="inlineStr">
         <is>
           <t>C23</t>
         </is>
       </c>
-      <c r="E83" s="16" t="inlineStr">
+      <c r="E83" s="17" t="inlineStr">
         <is>
           <t>S2 clip 22</t>
         </is>
       </c>
-      <c r="F83" s="16" t="n">
+      <c r="F83" s="17" t="n">
         <v>5</v>
       </c>
       <c r="G83" s="6" t="n">
@@ -6082,117 +6281,127 @@
       <c r="N83" s="6" t="inlineStr"/>
       <c r="O83" s="6" t="inlineStr"/>
       <c r="P83" s="6" t="inlineStr"/>
-      <c r="Q83" s="18" t="inlineStr">
-        <is>
-          <t>f2 · 100% · over</t>
-        </is>
-      </c>
-      <c r="R83" s="6" t="inlineStr"/>
-      <c r="S83" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q83" s="19" t="inlineStr">
+        <is>
+          <t>f2 · 100% · under</t>
+        </is>
+      </c>
+      <c r="R83" s="13" t="inlineStr">
+        <is>
+          <t>f3 · 100% · over</t>
+        </is>
+      </c>
+      <c r="S83" s="6" t="inlineStr"/>
       <c r="T83" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U83" s="6" t="inlineStr"/>
+      <c r="U83" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V83" s="6" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="19" t="n">
+      <c r="A84" s="20" t="n">
         <v>82</v>
       </c>
-      <c r="B84" s="20">
+      <c r="B84" s="21">
         <f>A84*1000/60</f>
         <v/>
       </c>
-      <c r="C84" s="19" t="inlineStr">
+      <c r="C84" s="20" t="inlineStr">
         <is>
           <t>E ระเบิดวง + ดาเมจ/ดีบัฟ</t>
         </is>
       </c>
-      <c r="D84" s="19" t="inlineStr">
+      <c r="D84" s="20" t="inlineStr">
         <is>
           <t>C23</t>
         </is>
       </c>
-      <c r="E84" s="19" t="inlineStr">
+      <c r="E84" s="20" t="inlineStr">
         <is>
           <t>S2 clip 22</t>
         </is>
       </c>
-      <c r="F84" s="19" t="n">
+      <c r="F84" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="G84" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" s="22">
+      <c r="G84" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="23">
         <f>G84/80</f>
         <v/>
       </c>
-      <c r="J84" s="21" t="n">
-        <v>390</v>
-      </c>
-      <c r="K84" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="L84" s="21" t="n">
-        <v>110</v>
-      </c>
-      <c r="M84" s="21" t="n">
-        <v>160</v>
-      </c>
-      <c r="N84" s="21" t="inlineStr">
+      <c r="J84" s="22" t="n">
+        <v>390</v>
+      </c>
+      <c r="K84" s="22" t="n">
+        <v>200</v>
+      </c>
+      <c r="L84" s="22" t="n">
+        <v>110</v>
+      </c>
+      <c r="M84" s="22" t="n">
+        <v>160</v>
+      </c>
+      <c r="N84" s="22" t="inlineStr">
         <is>
           <t>DAMAGE (magic AoE) / SLOW · ATK/CAST DOWN · ROOT*</t>
         </is>
       </c>
-      <c r="O84" s="21" t="inlineStr"/>
-      <c r="P84" s="21" t="inlineStr"/>
-      <c r="Q84" s="23" t="inlineStr">
-        <is>
-          <t>f2 · 100% · over</t>
-        </is>
-      </c>
-      <c r="R84" s="21" t="inlineStr"/>
-      <c r="S84" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T84" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U84" s="21" t="inlineStr">
+      <c r="O84" s="22" t="inlineStr"/>
+      <c r="P84" s="22" t="inlineStr"/>
+      <c r="Q84" s="24" t="inlineStr">
+        <is>
+          <t>f2 · 100% · under</t>
+        </is>
+      </c>
+      <c r="R84" s="25" t="inlineStr">
+        <is>
+          <t>f3 · 100% · over</t>
+        </is>
+      </c>
+      <c r="S84" s="22" t="inlineStr"/>
+      <c r="T84" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V84" s="22" t="inlineStr">
         <is>
           <t>burst peak f3 / *เฉพาะเป้าที่ติด Hex Mark</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="16" t="n">
+      <c r="A85" s="17" t="n">
         <v>83</v>
       </c>
-      <c r="B85" s="17">
+      <c r="B85" s="18">
         <f>A85*1000/60</f>
         <v/>
       </c>
-      <c r="C85" s="16" t="inlineStr">
+      <c r="C85" s="17" t="inlineStr">
         <is>
           <t>E ระเบิดวง + ดาเมจ/ดีบัฟ</t>
         </is>
       </c>
-      <c r="D85" s="16" t="inlineStr">
+      <c r="D85" s="17" t="inlineStr">
         <is>
           <t>C24</t>
         </is>
       </c>
-      <c r="E85" s="16" t="inlineStr">
+      <c r="E85" s="17" t="inlineStr">
         <is>
           <t>S2 clip 23</t>
         </is>
       </c>
-      <c r="F85" s="16" t="n">
+      <c r="F85" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G85" s="6" t="n">
@@ -6220,44 +6429,49 @@
       <c r="N85" s="6" t="inlineStr"/>
       <c r="O85" s="6" t="inlineStr"/>
       <c r="P85" s="6" t="inlineStr"/>
-      <c r="Q85" s="18" t="inlineStr">
-        <is>
-          <t>f3 · 100% · over</t>
-        </is>
-      </c>
-      <c r="R85" s="6" t="inlineStr"/>
-      <c r="S85" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q85" s="19" t="inlineStr">
+        <is>
+          <t>f3 · 100% · under</t>
+        </is>
+      </c>
+      <c r="R85" s="13" t="inlineStr">
+        <is>
+          <t>f4 · 100% · over</t>
+        </is>
+      </c>
+      <c r="S85" s="6" t="inlineStr"/>
       <c r="T85" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U85" s="6" t="inlineStr"/>
+      <c r="U85" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V85" s="6" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="16" t="n">
+      <c r="A86" s="17" t="n">
         <v>84</v>
       </c>
-      <c r="B86" s="17">
+      <c r="B86" s="18">
         <f>A86*1000/60</f>
         <v/>
       </c>
-      <c r="C86" s="16" t="inlineStr">
+      <c r="C86" s="17" t="inlineStr">
         <is>
           <t>E ระเบิดวง + ดาเมจ/ดีบัฟ</t>
         </is>
       </c>
-      <c r="D86" s="16" t="inlineStr">
+      <c r="D86" s="17" t="inlineStr">
         <is>
           <t>C24</t>
         </is>
       </c>
-      <c r="E86" s="16" t="inlineStr">
+      <c r="E86" s="17" t="inlineStr">
         <is>
           <t>S2 clip 23</t>
         </is>
       </c>
-      <c r="F86" s="16" t="n">
+      <c r="F86" s="17" t="n">
         <v>2</v>
       </c>
       <c r="G86" s="6" t="n">
@@ -6285,44 +6499,49 @@
       <c r="N86" s="6" t="inlineStr"/>
       <c r="O86" s="6" t="inlineStr"/>
       <c r="P86" s="6" t="inlineStr"/>
-      <c r="Q86" s="18" t="inlineStr">
-        <is>
-          <t>f3 · 100% · over</t>
-        </is>
-      </c>
-      <c r="R86" s="6" t="inlineStr"/>
-      <c r="S86" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q86" s="19" t="inlineStr">
+        <is>
+          <t>f3 · 100% · under</t>
+        </is>
+      </c>
+      <c r="R86" s="13" t="inlineStr">
+        <is>
+          <t>f4 · 100% · over</t>
+        </is>
+      </c>
+      <c r="S86" s="6" t="inlineStr"/>
       <c r="T86" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U86" s="6" t="inlineStr"/>
+      <c r="U86" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V86" s="6" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="16" t="n">
+      <c r="A87" s="17" t="n">
         <v>85</v>
       </c>
-      <c r="B87" s="17">
+      <c r="B87" s="18">
         <f>A87*1000/60</f>
         <v/>
       </c>
-      <c r="C87" s="16" t="inlineStr">
+      <c r="C87" s="17" t="inlineStr">
         <is>
           <t>E ระเบิดวง + ดาเมจ/ดีบัฟ</t>
         </is>
       </c>
-      <c r="D87" s="16" t="inlineStr">
+      <c r="D87" s="17" t="inlineStr">
         <is>
           <t>C24</t>
         </is>
       </c>
-      <c r="E87" s="16" t="inlineStr">
+      <c r="E87" s="17" t="inlineStr">
         <is>
           <t>S2 clip 23</t>
         </is>
       </c>
-      <c r="F87" s="16" t="n">
+      <c r="F87" s="17" t="n">
         <v>3</v>
       </c>
       <c r="G87" s="6" t="n">
@@ -6350,44 +6569,49 @@
       <c r="N87" s="6" t="inlineStr"/>
       <c r="O87" s="6" t="inlineStr"/>
       <c r="P87" s="6" t="inlineStr"/>
-      <c r="Q87" s="18" t="inlineStr">
-        <is>
-          <t>f3 · 100% · over</t>
-        </is>
-      </c>
-      <c r="R87" s="6" t="inlineStr"/>
-      <c r="S87" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q87" s="19" t="inlineStr">
+        <is>
+          <t>f3 · 100% · under</t>
+        </is>
+      </c>
+      <c r="R87" s="13" t="inlineStr">
+        <is>
+          <t>f5 · 100% · over</t>
+        </is>
+      </c>
+      <c r="S87" s="6" t="inlineStr"/>
       <c r="T87" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U87" s="6" t="inlineStr"/>
+      <c r="U87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V87" s="6" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="16" t="n">
+      <c r="A88" s="17" t="n">
         <v>86</v>
       </c>
-      <c r="B88" s="17">
+      <c r="B88" s="18">
         <f>A88*1000/60</f>
         <v/>
       </c>
-      <c r="C88" s="16" t="inlineStr">
+      <c r="C88" s="17" t="inlineStr">
         <is>
           <t>E ระเบิดวง + ดาเมจ/ดีบัฟ</t>
         </is>
       </c>
-      <c r="D88" s="16" t="inlineStr">
+      <c r="D88" s="17" t="inlineStr">
         <is>
           <t>C24</t>
         </is>
       </c>
-      <c r="E88" s="16" t="inlineStr">
+      <c r="E88" s="17" t="inlineStr">
         <is>
           <t>S2 clip 23</t>
         </is>
       </c>
-      <c r="F88" s="16" t="n">
+      <c r="F88" s="17" t="n">
         <v>4</v>
       </c>
       <c r="G88" s="6" t="n">
@@ -6415,44 +6639,49 @@
       <c r="N88" s="6" t="inlineStr"/>
       <c r="O88" s="6" t="inlineStr"/>
       <c r="P88" s="6" t="inlineStr"/>
-      <c r="Q88" s="18" t="inlineStr">
-        <is>
-          <t>f4 · 100% · over</t>
-        </is>
-      </c>
-      <c r="R88" s="6" t="inlineStr"/>
-      <c r="S88" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q88" s="19" t="inlineStr">
+        <is>
+          <t>f4 · 100% · under</t>
+        </is>
+      </c>
+      <c r="R88" s="13" t="inlineStr">
+        <is>
+          <t>f5 · 100% · over</t>
+        </is>
+      </c>
+      <c r="S88" s="6" t="inlineStr"/>
       <c r="T88" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U88" s="6" t="inlineStr"/>
+      <c r="U88" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V88" s="6" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="16" t="n">
+      <c r="A89" s="17" t="n">
         <v>87</v>
       </c>
-      <c r="B89" s="17">
+      <c r="B89" s="18">
         <f>A89*1000/60</f>
         <v/>
       </c>
-      <c r="C89" s="16" t="inlineStr">
+      <c r="C89" s="17" t="inlineStr">
         <is>
           <t>E ระเบิดวง + ดาเมจ/ดีบัฟ</t>
         </is>
       </c>
-      <c r="D89" s="16" t="inlineStr">
+      <c r="D89" s="17" t="inlineStr">
         <is>
           <t>C24</t>
         </is>
       </c>
-      <c r="E89" s="16" t="inlineStr">
+      <c r="E89" s="17" t="inlineStr">
         <is>
           <t>S2 clip 23</t>
         </is>
       </c>
-      <c r="F89" s="16" t="n">
+      <c r="F89" s="17" t="n">
         <v>5</v>
       </c>
       <c r="G89" s="6" t="n">
@@ -6480,44 +6709,49 @@
       <c r="N89" s="6" t="inlineStr"/>
       <c r="O89" s="6" t="inlineStr"/>
       <c r="P89" s="6" t="inlineStr"/>
-      <c r="Q89" s="18" t="inlineStr">
-        <is>
-          <t>f4 · 100% · over</t>
-        </is>
-      </c>
-      <c r="R89" s="6" t="inlineStr"/>
-      <c r="S89" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q89" s="19" t="inlineStr">
+        <is>
+          <t>f4 · 100% · under</t>
+        </is>
+      </c>
+      <c r="R89" s="13" t="inlineStr">
+        <is>
+          <t>f6 · 100% · over</t>
+        </is>
+      </c>
+      <c r="S89" s="6" t="inlineStr"/>
       <c r="T89" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U89" s="6" t="inlineStr"/>
+      <c r="U89" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" s="6" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="24" t="n">
+      <c r="A90" s="26" t="n">
         <v>88</v>
       </c>
-      <c r="B90" s="25">
+      <c r="B90" s="27">
         <f>A90*1000/60</f>
         <v/>
       </c>
-      <c r="C90" s="24" t="inlineStr">
+      <c r="C90" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D90" s="24" t="inlineStr">
+      <c r="D90" s="26" t="inlineStr">
         <is>
           <t>C25</t>
         </is>
       </c>
-      <c r="E90" s="24" t="inlineStr">
+      <c r="E90" s="26" t="inlineStr">
         <is>
           <t>S2 clip 24</t>
         </is>
       </c>
-      <c r="F90" s="24" t="n">
+      <c r="F90" s="26" t="n">
         <v>1</v>
       </c>
       <c r="G90" s="6" t="n">
@@ -6549,48 +6783,53 @@
       </c>
       <c r="O90" s="6" t="inlineStr"/>
       <c r="P90" s="6" t="inlineStr"/>
-      <c r="Q90" s="18" t="inlineStr">
-        <is>
-          <t>f4 · 100% · over</t>
-        </is>
-      </c>
-      <c r="R90" s="6" t="inlineStr"/>
-      <c r="S90" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q90" s="19" t="inlineStr">
+        <is>
+          <t>f4 · 100% · under</t>
+        </is>
+      </c>
+      <c r="R90" s="13" t="inlineStr">
+        <is>
+          <t>f6 · 100% · over</t>
+        </is>
+      </c>
+      <c r="S90" s="6" t="inlineStr"/>
       <c r="T90" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U90" s="6" t="inlineStr">
+      <c r="U90" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" s="6" t="inlineStr">
         <is>
           <t>C25</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="24" t="n">
+      <c r="A91" s="26" t="n">
         <v>89</v>
       </c>
-      <c r="B91" s="25">
+      <c r="B91" s="27">
         <f>A91*1000/60</f>
         <v/>
       </c>
-      <c r="C91" s="24" t="inlineStr">
+      <c r="C91" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D91" s="24" t="inlineStr">
+      <c r="D91" s="26" t="inlineStr">
         <is>
           <t>C25</t>
         </is>
       </c>
-      <c r="E91" s="24" t="inlineStr">
+      <c r="E91" s="26" t="inlineStr">
         <is>
           <t>S2 clip 24</t>
         </is>
       </c>
-      <c r="F91" s="24" t="n">
+      <c r="F91" s="26" t="n">
         <v>2</v>
       </c>
       <c r="G91" s="6" t="n">
@@ -6618,44 +6857,49 @@
       <c r="N91" s="6" t="inlineStr"/>
       <c r="O91" s="6" t="inlineStr"/>
       <c r="P91" s="6" t="inlineStr"/>
-      <c r="Q91" s="18" t="inlineStr">
-        <is>
-          <t>f5 · 100% · over</t>
-        </is>
-      </c>
-      <c r="R91" s="6" t="inlineStr"/>
-      <c r="S91" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q91" s="19" t="inlineStr">
+        <is>
+          <t>f5 · 100% · under</t>
+        </is>
+      </c>
+      <c r="R91" s="13" t="inlineStr">
+        <is>
+          <t>f7 · 100% · over</t>
+        </is>
+      </c>
+      <c r="S91" s="6" t="inlineStr"/>
       <c r="T91" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U91" s="6" t="inlineStr"/>
+      <c r="U91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" s="6" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="24" t="n">
+      <c r="A92" s="26" t="n">
         <v>90</v>
       </c>
-      <c r="B92" s="25">
+      <c r="B92" s="27">
         <f>A92*1000/60</f>
         <v/>
       </c>
-      <c r="C92" s="24" t="inlineStr">
+      <c r="C92" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D92" s="24" t="inlineStr">
+      <c r="D92" s="26" t="inlineStr">
         <is>
           <t>C25</t>
         </is>
       </c>
-      <c r="E92" s="24" t="inlineStr">
+      <c r="E92" s="26" t="inlineStr">
         <is>
           <t>S2 clip 24</t>
         </is>
       </c>
-      <c r="F92" s="24" t="n">
+      <c r="F92" s="26" t="n">
         <v>3</v>
       </c>
       <c r="G92" s="6" t="n">
@@ -6683,44 +6927,49 @@
       <c r="N92" s="6" t="inlineStr"/>
       <c r="O92" s="6" t="inlineStr"/>
       <c r="P92" s="6" t="inlineStr"/>
-      <c r="Q92" s="18" t="inlineStr">
-        <is>
-          <t>f5 · 100% · over</t>
-        </is>
-      </c>
-      <c r="R92" s="6" t="inlineStr"/>
-      <c r="S92" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q92" s="19" t="inlineStr">
+        <is>
+          <t>f5 · 100% · under</t>
+        </is>
+      </c>
+      <c r="R92" s="13" t="inlineStr">
+        <is>
+          <t>f7 · 100% · over</t>
+        </is>
+      </c>
+      <c r="S92" s="6" t="inlineStr"/>
       <c r="T92" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U92" s="6" t="inlineStr"/>
+      <c r="U92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V92" s="6" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="24" t="n">
+      <c r="A93" s="26" t="n">
         <v>91</v>
       </c>
-      <c r="B93" s="25">
+      <c r="B93" s="27">
         <f>A93*1000/60</f>
         <v/>
       </c>
-      <c r="C93" s="24" t="inlineStr">
+      <c r="C93" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D93" s="24" t="inlineStr">
+      <c r="D93" s="26" t="inlineStr">
         <is>
           <t>C25</t>
         </is>
       </c>
-      <c r="E93" s="24" t="inlineStr">
+      <c r="E93" s="26" t="inlineStr">
         <is>
           <t>S2 clip 24</t>
         </is>
       </c>
-      <c r="F93" s="24" t="n">
+      <c r="F93" s="26" t="n">
         <v>4</v>
       </c>
       <c r="G93" s="6" t="n">
@@ -6748,44 +6997,49 @@
       <c r="N93" s="6" t="inlineStr"/>
       <c r="O93" s="6" t="inlineStr"/>
       <c r="P93" s="6" t="inlineStr"/>
-      <c r="Q93" s="18" t="inlineStr">
-        <is>
-          <t>f5 · 100% · over</t>
-        </is>
-      </c>
-      <c r="R93" s="6" t="inlineStr"/>
-      <c r="S93" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q93" s="19" t="inlineStr">
+        <is>
+          <t>f5 · 100% · under</t>
+        </is>
+      </c>
+      <c r="R93" s="13" t="inlineStr">
+        <is>
+          <t>f7 · 100% · over</t>
+        </is>
+      </c>
+      <c r="S93" s="6" t="inlineStr"/>
       <c r="T93" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U93" s="6" t="inlineStr"/>
+      <c r="U93" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" s="6" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="24" t="n">
+      <c r="A94" s="26" t="n">
         <v>92</v>
       </c>
-      <c r="B94" s="25">
+      <c r="B94" s="27">
         <f>A94*1000/60</f>
         <v/>
       </c>
-      <c r="C94" s="24" t="inlineStr">
+      <c r="C94" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D94" s="24" t="inlineStr">
+      <c r="D94" s="26" t="inlineStr">
         <is>
           <t>C26</t>
         </is>
       </c>
-      <c r="E94" s="24" t="inlineStr">
+      <c r="E94" s="26" t="inlineStr">
         <is>
           <t>S2 clip 25</t>
         </is>
       </c>
-      <c r="F94" s="24" t="n">
+      <c r="F94" s="26" t="n">
         <v>1</v>
       </c>
       <c r="G94" s="6" t="n">
@@ -6813,44 +7067,49 @@
       <c r="N94" s="6" t="inlineStr"/>
       <c r="O94" s="6" t="inlineStr"/>
       <c r="P94" s="6" t="inlineStr"/>
-      <c r="Q94" s="18" t="inlineStr">
-        <is>
-          <t>f6 · 100% · over</t>
-        </is>
-      </c>
-      <c r="R94" s="6" t="inlineStr"/>
-      <c r="S94" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q94" s="19" t="inlineStr">
+        <is>
+          <t>f6 · 100% · under</t>
+        </is>
+      </c>
+      <c r="R94" s="13" t="inlineStr">
+        <is>
+          <t>f7 · 95% · over</t>
+        </is>
+      </c>
+      <c r="S94" s="6" t="inlineStr"/>
       <c r="T94" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U94" s="6" t="inlineStr"/>
+      <c r="U94" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V94" s="6" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="24" t="n">
+      <c r="A95" s="26" t="n">
         <v>93</v>
       </c>
-      <c r="B95" s="25">
+      <c r="B95" s="27">
         <f>A95*1000/60</f>
         <v/>
       </c>
-      <c r="C95" s="24" t="inlineStr">
+      <c r="C95" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D95" s="24" t="inlineStr">
+      <c r="D95" s="26" t="inlineStr">
         <is>
           <t>C26</t>
         </is>
       </c>
-      <c r="E95" s="24" t="inlineStr">
+      <c r="E95" s="26" t="inlineStr">
         <is>
           <t>S2 clip 25</t>
         </is>
       </c>
-      <c r="F95" s="24" t="n">
+      <c r="F95" s="26" t="n">
         <v>2</v>
       </c>
       <c r="G95" s="6" t="n">
@@ -6878,44 +7137,49 @@
       <c r="N95" s="6" t="inlineStr"/>
       <c r="O95" s="6" t="inlineStr"/>
       <c r="P95" s="6" t="inlineStr"/>
-      <c r="Q95" s="18" t="inlineStr">
-        <is>
-          <t>f6 · 100% · over</t>
-        </is>
-      </c>
-      <c r="R95" s="6" t="inlineStr"/>
-      <c r="S95" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q95" s="19" t="inlineStr">
+        <is>
+          <t>f6 · 100% · under</t>
+        </is>
+      </c>
+      <c r="R95" s="13" t="inlineStr">
+        <is>
+          <t>f7 · 81% · over</t>
+        </is>
+      </c>
+      <c r="S95" s="6" t="inlineStr"/>
       <c r="T95" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U95" s="6" t="inlineStr"/>
+      <c r="U95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V95" s="6" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="24" t="n">
+      <c r="A96" s="26" t="n">
         <v>94</v>
       </c>
-      <c r="B96" s="25">
+      <c r="B96" s="27">
         <f>A96*1000/60</f>
         <v/>
       </c>
-      <c r="C96" s="24" t="inlineStr">
+      <c r="C96" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D96" s="24" t="inlineStr">
+      <c r="D96" s="26" t="inlineStr">
         <is>
           <t>C26</t>
         </is>
       </c>
-      <c r="E96" s="24" t="inlineStr">
+      <c r="E96" s="26" t="inlineStr">
         <is>
           <t>S2 clip 25</t>
         </is>
       </c>
-      <c r="F96" s="24" t="n">
+      <c r="F96" s="26" t="n">
         <v>3</v>
       </c>
       <c r="G96" s="6" t="n">
@@ -6943,44 +7207,49 @@
       <c r="N96" s="6" t="inlineStr"/>
       <c r="O96" s="6" t="inlineStr"/>
       <c r="P96" s="6" t="inlineStr"/>
-      <c r="Q96" s="18" t="inlineStr">
-        <is>
-          <t>f6 · 100% · over</t>
-        </is>
-      </c>
-      <c r="R96" s="6" t="inlineStr"/>
-      <c r="S96" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q96" s="19" t="inlineStr">
+        <is>
+          <t>f6 · 100% · under</t>
+        </is>
+      </c>
+      <c r="R96" s="13" t="inlineStr">
+        <is>
+          <t>f7 · 58% · over</t>
+        </is>
+      </c>
+      <c r="S96" s="6" t="inlineStr"/>
       <c r="T96" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U96" s="6" t="inlineStr"/>
+      <c r="U96" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" s="6" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="24" t="n">
+      <c r="A97" s="26" t="n">
         <v>95</v>
       </c>
-      <c r="B97" s="25">
+      <c r="B97" s="27">
         <f>A97*1000/60</f>
         <v/>
       </c>
-      <c r="C97" s="24" t="inlineStr">
+      <c r="C97" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D97" s="24" t="inlineStr">
+      <c r="D97" s="26" t="inlineStr">
         <is>
           <t>C26</t>
         </is>
       </c>
-      <c r="E97" s="24" t="inlineStr">
+      <c r="E97" s="26" t="inlineStr">
         <is>
           <t>S2 clip 25</t>
         </is>
       </c>
-      <c r="F97" s="24" t="n">
+      <c r="F97" s="26" t="n">
         <v>4</v>
       </c>
       <c r="G97" s="6" t="n">
@@ -7008,44 +7277,49 @@
       <c r="N97" s="6" t="inlineStr"/>
       <c r="O97" s="6" t="inlineStr"/>
       <c r="P97" s="6" t="inlineStr"/>
-      <c r="Q97" s="18" t="inlineStr">
-        <is>
-          <t>f7 · 100% · over</t>
-        </is>
-      </c>
-      <c r="R97" s="6" t="inlineStr"/>
-      <c r="S97" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q97" s="19" t="inlineStr">
+        <is>
+          <t>f7 · 100% · under</t>
+        </is>
+      </c>
+      <c r="R97" s="13" t="inlineStr">
+        <is>
+          <t>f7 · 27% · over</t>
+        </is>
+      </c>
+      <c r="S97" s="6" t="inlineStr"/>
       <c r="T97" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U97" s="6" t="inlineStr"/>
+      <c r="U97" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V97" s="6" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="24" t="n">
+      <c r="A98" s="26" t="n">
         <v>96</v>
       </c>
-      <c r="B98" s="25">
+      <c r="B98" s="27">
         <f>A98*1000/60</f>
         <v/>
       </c>
-      <c r="C98" s="24" t="inlineStr">
+      <c r="C98" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D98" s="24" t="inlineStr">
+      <c r="D98" s="26" t="inlineStr">
         <is>
           <t>C27</t>
         </is>
       </c>
-      <c r="E98" s="24" t="inlineStr">
+      <c r="E98" s="26" t="inlineStr">
         <is>
           <t>S2 clip 26</t>
         </is>
       </c>
-      <c r="F98" s="24" t="n">
+      <c r="F98" s="26" t="n">
         <v>1</v>
       </c>
       <c r="G98" s="6" t="n">
@@ -7073,44 +7347,45 @@
       <c r="N98" s="6" t="inlineStr"/>
       <c r="O98" s="6" t="inlineStr"/>
       <c r="P98" s="6" t="inlineStr"/>
-      <c r="Q98" s="18" t="inlineStr">
-        <is>
-          <t>f7 · 100% · over</t>
+      <c r="Q98" s="19" t="inlineStr">
+        <is>
+          <t>f7 · 100% · under</t>
         </is>
       </c>
       <c r="R98" s="6" t="inlineStr"/>
-      <c r="S98" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S98" s="6" t="inlineStr"/>
       <c r="T98" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U98" s="6" t="inlineStr"/>
+      <c r="U98" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V98" s="6" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="24" t="n">
+      <c r="A99" s="26" t="n">
         <v>97</v>
       </c>
-      <c r="B99" s="25">
+      <c r="B99" s="27">
         <f>A99*1000/60</f>
         <v/>
       </c>
-      <c r="C99" s="24" t="inlineStr">
+      <c r="C99" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D99" s="24" t="inlineStr">
+      <c r="D99" s="26" t="inlineStr">
         <is>
           <t>C27</t>
         </is>
       </c>
-      <c r="E99" s="24" t="inlineStr">
+      <c r="E99" s="26" t="inlineStr">
         <is>
           <t>S2 clip 26</t>
         </is>
       </c>
-      <c r="F99" s="24" t="n">
+      <c r="F99" s="26" t="n">
         <v>2</v>
       </c>
       <c r="G99" s="6" t="n">
@@ -7138,44 +7413,45 @@
       <c r="N99" s="6" t="inlineStr"/>
       <c r="O99" s="6" t="inlineStr"/>
       <c r="P99" s="6" t="inlineStr"/>
-      <c r="Q99" s="18" t="inlineStr">
-        <is>
-          <t>f7 · 100% · over</t>
+      <c r="Q99" s="19" t="inlineStr">
+        <is>
+          <t>f7 · 100% · under</t>
         </is>
       </c>
       <c r="R99" s="6" t="inlineStr"/>
-      <c r="S99" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S99" s="6" t="inlineStr"/>
       <c r="T99" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U99" s="6" t="inlineStr"/>
+      <c r="U99" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V99" s="6" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="24" t="n">
+      <c r="A100" s="26" t="n">
         <v>98</v>
       </c>
-      <c r="B100" s="25">
+      <c r="B100" s="27">
         <f>A100*1000/60</f>
         <v/>
       </c>
-      <c r="C100" s="24" t="inlineStr">
+      <c r="C100" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D100" s="24" t="inlineStr">
+      <c r="D100" s="26" t="inlineStr">
         <is>
           <t>C27</t>
         </is>
       </c>
-      <c r="E100" s="24" t="inlineStr">
+      <c r="E100" s="26" t="inlineStr">
         <is>
           <t>S2 clip 26</t>
         </is>
       </c>
-      <c r="F100" s="24" t="n">
+      <c r="F100" s="26" t="n">
         <v>3</v>
       </c>
       <c r="G100" s="6" t="n">
@@ -7203,44 +7479,45 @@
       <c r="N100" s="6" t="inlineStr"/>
       <c r="O100" s="6" t="inlineStr"/>
       <c r="P100" s="6" t="inlineStr"/>
-      <c r="Q100" s="18" t="inlineStr">
-        <is>
-          <t>f8 · 100% · over</t>
+      <c r="Q100" s="19" t="inlineStr">
+        <is>
+          <t>f8 · 100% · under</t>
         </is>
       </c>
       <c r="R100" s="6" t="inlineStr"/>
-      <c r="S100" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S100" s="6" t="inlineStr"/>
       <c r="T100" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U100" s="6" t="inlineStr"/>
+      <c r="U100" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V100" s="6" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="24" t="n">
+      <c r="A101" s="26" t="n">
         <v>99</v>
       </c>
-      <c r="B101" s="25">
+      <c r="B101" s="27">
         <f>A101*1000/60</f>
         <v/>
       </c>
-      <c r="C101" s="24" t="inlineStr">
+      <c r="C101" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D101" s="24" t="inlineStr">
+      <c r="D101" s="26" t="inlineStr">
         <is>
           <t>C27</t>
         </is>
       </c>
-      <c r="E101" s="24" t="inlineStr">
+      <c r="E101" s="26" t="inlineStr">
         <is>
           <t>S2 clip 26</t>
         </is>
       </c>
-      <c r="F101" s="24" t="n">
+      <c r="F101" s="26" t="n">
         <v>4</v>
       </c>
       <c r="G101" s="6" t="n">
@@ -7268,44 +7545,45 @@
       <c r="N101" s="6" t="inlineStr"/>
       <c r="O101" s="6" t="inlineStr"/>
       <c r="P101" s="6" t="inlineStr"/>
-      <c r="Q101" s="18" t="inlineStr">
-        <is>
-          <t>f8 · 100% · over</t>
+      <c r="Q101" s="19" t="inlineStr">
+        <is>
+          <t>f8 · 100% · under</t>
         </is>
       </c>
       <c r="R101" s="6" t="inlineStr"/>
-      <c r="S101" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S101" s="6" t="inlineStr"/>
       <c r="T101" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U101" s="6" t="inlineStr"/>
+      <c r="U101" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" s="6" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="24" t="n">
+      <c r="A102" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="B102" s="25">
+      <c r="B102" s="27">
         <f>A102*1000/60</f>
         <v/>
       </c>
-      <c r="C102" s="24" t="inlineStr">
+      <c r="C102" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D102" s="24" t="inlineStr">
+      <c r="D102" s="26" t="inlineStr">
         <is>
           <t>C27</t>
         </is>
       </c>
-      <c r="E102" s="24" t="inlineStr">
+      <c r="E102" s="26" t="inlineStr">
         <is>
           <t>S2 clip 26</t>
         </is>
       </c>
-      <c r="F102" s="24" t="n">
+      <c r="F102" s="26" t="n">
         <v>5</v>
       </c>
       <c r="G102" s="6" t="n">
@@ -7333,44 +7611,45 @@
       <c r="N102" s="6" t="inlineStr"/>
       <c r="O102" s="6" t="inlineStr"/>
       <c r="P102" s="6" t="inlineStr"/>
-      <c r="Q102" s="18" t="inlineStr">
-        <is>
-          <t>f8 · 100% · over</t>
+      <c r="Q102" s="19" t="inlineStr">
+        <is>
+          <t>f8 · 100% · under</t>
         </is>
       </c>
       <c r="R102" s="6" t="inlineStr"/>
-      <c r="S102" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S102" s="6" t="inlineStr"/>
       <c r="T102" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U102" s="6" t="inlineStr"/>
+      <c r="U102" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" s="6" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="24" t="n">
+      <c r="A103" s="26" t="n">
         <v>101</v>
       </c>
-      <c r="B103" s="25">
+      <c r="B103" s="27">
         <f>A103*1000/60</f>
         <v/>
       </c>
-      <c r="C103" s="24" t="inlineStr">
+      <c r="C103" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D103" s="24" t="inlineStr">
+      <c r="D103" s="26" t="inlineStr">
         <is>
           <t>C28</t>
         </is>
       </c>
-      <c r="E103" s="24" t="inlineStr">
+      <c r="E103" s="26" t="inlineStr">
         <is>
           <t>S2 clip 27</t>
         </is>
       </c>
-      <c r="F103" s="24" t="n">
+      <c r="F103" s="26" t="n">
         <v>1</v>
       </c>
       <c r="G103" s="6" t="n">
@@ -7398,44 +7677,45 @@
       <c r="N103" s="6" t="inlineStr"/>
       <c r="O103" s="6" t="inlineStr"/>
       <c r="P103" s="6" t="inlineStr"/>
-      <c r="Q103" s="18" t="inlineStr">
-        <is>
-          <t>f8 · 99% · over</t>
+      <c r="Q103" s="19" t="inlineStr">
+        <is>
+          <t>f8 · 99% · under</t>
         </is>
       </c>
       <c r="R103" s="6" t="inlineStr"/>
-      <c r="S103" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S103" s="6" t="inlineStr"/>
       <c r="T103" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U103" s="6" t="inlineStr"/>
+      <c r="U103" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V103" s="6" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="24" t="n">
+      <c r="A104" s="26" t="n">
         <v>102</v>
       </c>
-      <c r="B104" s="25">
+      <c r="B104" s="27">
         <f>A104*1000/60</f>
         <v/>
       </c>
-      <c r="C104" s="24" t="inlineStr">
+      <c r="C104" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D104" s="24" t="inlineStr">
+      <c r="D104" s="26" t="inlineStr">
         <is>
           <t>C28</t>
         </is>
       </c>
-      <c r="E104" s="24" t="inlineStr">
+      <c r="E104" s="26" t="inlineStr">
         <is>
           <t>S2 clip 27</t>
         </is>
       </c>
-      <c r="F104" s="24" t="n">
+      <c r="F104" s="26" t="n">
         <v>2</v>
       </c>
       <c r="G104" s="6" t="n">
@@ -7463,44 +7743,45 @@
       <c r="N104" s="6" t="inlineStr"/>
       <c r="O104" s="6" t="inlineStr"/>
       <c r="P104" s="6" t="inlineStr"/>
-      <c r="Q104" s="18" t="inlineStr">
-        <is>
-          <t>f8 · 96% · over</t>
+      <c r="Q104" s="19" t="inlineStr">
+        <is>
+          <t>f8 · 96% · under</t>
         </is>
       </c>
       <c r="R104" s="6" t="inlineStr"/>
-      <c r="S104" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S104" s="6" t="inlineStr"/>
       <c r="T104" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U104" s="6" t="inlineStr"/>
+      <c r="U104" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V104" s="6" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="24" t="n">
+      <c r="A105" s="26" t="n">
         <v>103</v>
       </c>
-      <c r="B105" s="25">
+      <c r="B105" s="27">
         <f>A105*1000/60</f>
         <v/>
       </c>
-      <c r="C105" s="24" t="inlineStr">
+      <c r="C105" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D105" s="24" t="inlineStr">
+      <c r="D105" s="26" t="inlineStr">
         <is>
           <t>C28</t>
         </is>
       </c>
-      <c r="E105" s="24" t="inlineStr">
+      <c r="E105" s="26" t="inlineStr">
         <is>
           <t>S2 clip 27</t>
         </is>
       </c>
-      <c r="F105" s="24" t="n">
+      <c r="F105" s="26" t="n">
         <v>3</v>
       </c>
       <c r="G105" s="6" t="n">
@@ -7528,44 +7809,45 @@
       <c r="N105" s="6" t="inlineStr"/>
       <c r="O105" s="6" t="inlineStr"/>
       <c r="P105" s="6" t="inlineStr"/>
-      <c r="Q105" s="18" t="inlineStr">
-        <is>
-          <t>f8 · 90% · over</t>
+      <c r="Q105" s="19" t="inlineStr">
+        <is>
+          <t>f8 · 90% · under</t>
         </is>
       </c>
       <c r="R105" s="6" t="inlineStr"/>
-      <c r="S105" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S105" s="6" t="inlineStr"/>
       <c r="T105" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U105" s="6" t="inlineStr"/>
+      <c r="U105" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V105" s="6" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="24" t="n">
+      <c r="A106" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="B106" s="25">
+      <c r="B106" s="27">
         <f>A106*1000/60</f>
         <v/>
       </c>
-      <c r="C106" s="24" t="inlineStr">
+      <c r="C106" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D106" s="24" t="inlineStr">
+      <c r="D106" s="26" t="inlineStr">
         <is>
           <t>C28</t>
         </is>
       </c>
-      <c r="E106" s="24" t="inlineStr">
+      <c r="E106" s="26" t="inlineStr">
         <is>
           <t>S2 clip 27</t>
         </is>
       </c>
-      <c r="F106" s="24" t="n">
+      <c r="F106" s="26" t="n">
         <v>4</v>
       </c>
       <c r="G106" s="6" t="n">
@@ -7593,44 +7875,45 @@
       <c r="N106" s="6" t="inlineStr"/>
       <c r="O106" s="6" t="inlineStr"/>
       <c r="P106" s="6" t="inlineStr"/>
-      <c r="Q106" s="18" t="inlineStr">
-        <is>
-          <t>f8 · 82% · over</t>
+      <c r="Q106" s="19" t="inlineStr">
+        <is>
+          <t>f8 · 82% · under</t>
         </is>
       </c>
       <c r="R106" s="6" t="inlineStr"/>
-      <c r="S106" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S106" s="6" t="inlineStr"/>
       <c r="T106" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U106" s="6" t="inlineStr"/>
+      <c r="U106" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" s="6" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="24" t="n">
+      <c r="A107" s="26" t="n">
         <v>105</v>
       </c>
-      <c r="B107" s="25">
+      <c r="B107" s="27">
         <f>A107*1000/60</f>
         <v/>
       </c>
-      <c r="C107" s="24" t="inlineStr">
+      <c r="C107" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D107" s="24" t="inlineStr">
+      <c r="D107" s="26" t="inlineStr">
         <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="E107" s="24" t="inlineStr">
+      <c r="E107" s="26" t="inlineStr">
         <is>
           <t>S2 clip 28</t>
         </is>
       </c>
-      <c r="F107" s="24" t="n">
+      <c r="F107" s="26" t="n">
         <v>1</v>
       </c>
       <c r="G107" s="6" t="n">
@@ -7658,44 +7941,45 @@
       <c r="N107" s="6" t="inlineStr"/>
       <c r="O107" s="6" t="inlineStr"/>
       <c r="P107" s="6" t="inlineStr"/>
-      <c r="Q107" s="18" t="inlineStr">
-        <is>
-          <t>f8 · 72% · over</t>
+      <c r="Q107" s="19" t="inlineStr">
+        <is>
+          <t>f8 · 72% · under</t>
         </is>
       </c>
       <c r="R107" s="6" t="inlineStr"/>
-      <c r="S107" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S107" s="6" t="inlineStr"/>
       <c r="T107" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U107" s="6" t="inlineStr"/>
+      <c r="U107" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V107" s="6" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="24" t="n">
+      <c r="A108" s="26" t="n">
         <v>106</v>
       </c>
-      <c r="B108" s="25">
+      <c r="B108" s="27">
         <f>A108*1000/60</f>
         <v/>
       </c>
-      <c r="C108" s="24" t="inlineStr">
+      <c r="C108" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D108" s="24" t="inlineStr">
+      <c r="D108" s="26" t="inlineStr">
         <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="E108" s="24" t="inlineStr">
+      <c r="E108" s="26" t="inlineStr">
         <is>
           <t>S2 clip 28</t>
         </is>
       </c>
-      <c r="F108" s="24" t="n">
+      <c r="F108" s="26" t="n">
         <v>2</v>
       </c>
       <c r="G108" s="6" t="n">
@@ -7723,44 +8007,45 @@
       <c r="N108" s="6" t="inlineStr"/>
       <c r="O108" s="6" t="inlineStr"/>
       <c r="P108" s="6" t="inlineStr"/>
-      <c r="Q108" s="18" t="inlineStr">
-        <is>
-          <t>f8 · 58% · over</t>
+      <c r="Q108" s="19" t="inlineStr">
+        <is>
+          <t>f8 · 58% · under</t>
         </is>
       </c>
       <c r="R108" s="6" t="inlineStr"/>
-      <c r="S108" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S108" s="6" t="inlineStr"/>
       <c r="T108" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U108" s="6" t="inlineStr"/>
+      <c r="U108" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" s="6" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="24" t="n">
+      <c r="A109" s="26" t="n">
         <v>107</v>
       </c>
-      <c r="B109" s="25">
+      <c r="B109" s="27">
         <f>A109*1000/60</f>
         <v/>
       </c>
-      <c r="C109" s="24" t="inlineStr">
+      <c r="C109" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D109" s="24" t="inlineStr">
+      <c r="D109" s="26" t="inlineStr">
         <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="E109" s="24" t="inlineStr">
+      <c r="E109" s="26" t="inlineStr">
         <is>
           <t>S2 clip 28</t>
         </is>
       </c>
-      <c r="F109" s="24" t="n">
+      <c r="F109" s="26" t="n">
         <v>3</v>
       </c>
       <c r="G109" s="6" t="n">
@@ -7788,44 +8073,45 @@
       <c r="N109" s="6" t="inlineStr"/>
       <c r="O109" s="6" t="inlineStr"/>
       <c r="P109" s="6" t="inlineStr"/>
-      <c r="Q109" s="18" t="inlineStr">
-        <is>
-          <t>f8 · 43% · over</t>
+      <c r="Q109" s="19" t="inlineStr">
+        <is>
+          <t>f8 · 43% · under</t>
         </is>
       </c>
       <c r="R109" s="6" t="inlineStr"/>
-      <c r="S109" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S109" s="6" t="inlineStr"/>
       <c r="T109" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U109" s="6" t="inlineStr"/>
+      <c r="U109" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" s="6" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="24" t="n">
+      <c r="A110" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="B110" s="25">
+      <c r="B110" s="27">
         <f>A110*1000/60</f>
         <v/>
       </c>
-      <c r="C110" s="24" t="inlineStr">
+      <c r="C110" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D110" s="24" t="inlineStr">
+      <c r="D110" s="26" t="inlineStr">
         <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="E110" s="24" t="inlineStr">
+      <c r="E110" s="26" t="inlineStr">
         <is>
           <t>S2 clip 28</t>
         </is>
       </c>
-      <c r="F110" s="24" t="n">
+      <c r="F110" s="26" t="n">
         <v>4</v>
       </c>
       <c r="G110" s="6" t="n">
@@ -7853,44 +8139,45 @@
       <c r="N110" s="6" t="inlineStr"/>
       <c r="O110" s="6" t="inlineStr"/>
       <c r="P110" s="6" t="inlineStr"/>
-      <c r="Q110" s="18" t="inlineStr">
-        <is>
-          <t>f8 · 25% · over</t>
+      <c r="Q110" s="19" t="inlineStr">
+        <is>
+          <t>f8 · 25% · under</t>
         </is>
       </c>
       <c r="R110" s="6" t="inlineStr"/>
-      <c r="S110" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S110" s="6" t="inlineStr"/>
       <c r="T110" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U110" s="6" t="inlineStr"/>
+      <c r="U110" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V110" s="6" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="24" t="n">
+      <c r="A111" s="26" t="n">
         <v>109</v>
       </c>
-      <c r="B111" s="25">
+      <c r="B111" s="27">
         <f>A111*1000/60</f>
         <v/>
       </c>
-      <c r="C111" s="24" t="inlineStr">
+      <c r="C111" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D111" s="24" t="inlineStr">
+      <c r="D111" s="26" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="E111" s="24" t="inlineStr">
+      <c r="E111" s="26" t="inlineStr">
         <is>
           <t>S2 clip 29</t>
         </is>
       </c>
-      <c r="F111" s="24" t="n">
+      <c r="F111" s="26" t="n">
         <v>1</v>
       </c>
       <c r="G111" s="6" t="n">
@@ -7918,44 +8205,45 @@
       <c r="N111" s="6" t="inlineStr"/>
       <c r="O111" s="6" t="inlineStr"/>
       <c r="P111" s="6" t="inlineStr"/>
-      <c r="Q111" s="18" t="inlineStr">
-        <is>
-          <t>f8 · 4% · over</t>
+      <c r="Q111" s="19" t="inlineStr">
+        <is>
+          <t>f8 · 4% · under</t>
         </is>
       </c>
       <c r="R111" s="6" t="inlineStr"/>
-      <c r="S111" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S111" s="6" t="inlineStr"/>
       <c r="T111" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U111" s="6" t="inlineStr"/>
+      <c r="U111" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V111" s="6" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="24" t="n">
-        <v>110</v>
-      </c>
-      <c r="B112" s="25">
+      <c r="A112" s="26" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" s="27">
         <f>A112*1000/60</f>
         <v/>
       </c>
-      <c r="C112" s="24" t="inlineStr">
+      <c r="C112" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D112" s="24" t="inlineStr">
+      <c r="D112" s="26" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="E112" s="24" t="inlineStr">
+      <c r="E112" s="26" t="inlineStr">
         <is>
           <t>S2 clip 29</t>
         </is>
       </c>
-      <c r="F112" s="24" t="n">
+      <c r="F112" s="26" t="n">
         <v>2</v>
       </c>
       <c r="G112" s="6" t="n">
@@ -7985,38 +8273,39 @@
       <c r="P112" s="6" t="inlineStr"/>
       <c r="Q112" s="6" t="inlineStr"/>
       <c r="R112" s="6" t="inlineStr"/>
-      <c r="S112" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S112" s="6" t="inlineStr"/>
       <c r="T112" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U112" s="6" t="inlineStr"/>
+      <c r="U112" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V112" s="6" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="24" t="n">
+      <c r="A113" s="26" t="n">
         <v>111</v>
       </c>
-      <c r="B113" s="25">
+      <c r="B113" s="27">
         <f>A113*1000/60</f>
         <v/>
       </c>
-      <c r="C113" s="24" t="inlineStr">
+      <c r="C113" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D113" s="24" t="inlineStr">
+      <c r="D113" s="26" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="E113" s="24" t="inlineStr">
+      <c r="E113" s="26" t="inlineStr">
         <is>
           <t>S2 clip 29</t>
         </is>
       </c>
-      <c r="F113" s="24" t="n">
+      <c r="F113" s="26" t="n">
         <v>3</v>
       </c>
       <c r="G113" s="6" t="n">
@@ -8046,38 +8335,39 @@
       <c r="P113" s="6" t="inlineStr"/>
       <c r="Q113" s="6" t="inlineStr"/>
       <c r="R113" s="6" t="inlineStr"/>
-      <c r="S113" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S113" s="6" t="inlineStr"/>
       <c r="T113" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U113" s="6" t="inlineStr"/>
+      <c r="U113" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V113" s="6" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="24" t="n">
+      <c r="A114" s="26" t="n">
         <v>112</v>
       </c>
-      <c r="B114" s="25">
+      <c r="B114" s="27">
         <f>A114*1000/60</f>
         <v/>
       </c>
-      <c r="C114" s="24" t="inlineStr">
+      <c r="C114" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D114" s="24" t="inlineStr">
+      <c r="D114" s="26" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="E114" s="24" t="inlineStr">
+      <c r="E114" s="26" t="inlineStr">
         <is>
           <t>S2 clip 29</t>
         </is>
       </c>
-      <c r="F114" s="24" t="n">
+      <c r="F114" s="26" t="n">
         <v>4</v>
       </c>
       <c r="G114" s="6" t="n">
@@ -8107,38 +8397,39 @@
       <c r="P114" s="6" t="inlineStr"/>
       <c r="Q114" s="6" t="inlineStr"/>
       <c r="R114" s="6" t="inlineStr"/>
-      <c r="S114" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S114" s="6" t="inlineStr"/>
       <c r="T114" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U114" s="6" t="inlineStr"/>
+      <c r="U114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V114" s="6" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="24" t="n">
+      <c r="A115" s="26" t="n">
         <v>113</v>
       </c>
-      <c r="B115" s="25">
+      <c r="B115" s="27">
         <f>A115*1000/60</f>
         <v/>
       </c>
-      <c r="C115" s="24" t="inlineStr">
+      <c r="C115" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D115" s="24" t="inlineStr">
+      <c r="D115" s="26" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="E115" s="24" t="inlineStr">
+      <c r="E115" s="26" t="inlineStr">
         <is>
           <t>S2 clip 29</t>
         </is>
       </c>
-      <c r="F115" s="24" t="n">
+      <c r="F115" s="26" t="n">
         <v>5</v>
       </c>
       <c r="G115" s="6" t="n">
@@ -8172,42 +8463,43 @@
       <c r="P115" s="6" t="inlineStr"/>
       <c r="Q115" s="6" t="inlineStr"/>
       <c r="R115" s="6" t="inlineStr"/>
-      <c r="S115" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S115" s="6" t="inlineStr"/>
       <c r="T115" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U115" s="6" t="inlineStr">
+      <c r="U115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V115" s="6" t="inlineStr">
         <is>
           <t>clip end 1.89s</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="24" t="n">
+      <c r="A116" s="26" t="n">
         <v>114</v>
       </c>
-      <c r="B116" s="25">
+      <c r="B116" s="27">
         <f>A116*1000/60</f>
         <v/>
       </c>
-      <c r="C116" s="24" t="inlineStr">
+      <c r="C116" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D116" s="24" t="inlineStr">
+      <c r="D116" s="26" t="inlineStr">
         <is>
           <t>C31</t>
         </is>
       </c>
-      <c r="E116" s="24" t="inlineStr">
+      <c r="E116" s="26" t="inlineStr">
         <is>
           <t>idle</t>
         </is>
       </c>
-      <c r="F116" s="24" t="n">
+      <c r="F116" s="26" t="n">
         <v>1</v>
       </c>
       <c r="G116" s="6" t="n">
@@ -8237,38 +8529,39 @@
       <c r="P116" s="6" t="inlineStr"/>
       <c r="Q116" s="6" t="inlineStr"/>
       <c r="R116" s="6" t="inlineStr"/>
-      <c r="S116" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S116" s="6" t="inlineStr"/>
       <c r="T116" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U116" s="6" t="inlineStr"/>
+      <c r="U116" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V116" s="6" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="24" t="n">
+      <c r="A117" s="26" t="n">
         <v>115</v>
       </c>
-      <c r="B117" s="25">
+      <c r="B117" s="27">
         <f>A117*1000/60</f>
         <v/>
       </c>
-      <c r="C117" s="24" t="inlineStr">
+      <c r="C117" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D117" s="24" t="inlineStr">
+      <c r="D117" s="26" t="inlineStr">
         <is>
           <t>C31</t>
         </is>
       </c>
-      <c r="E117" s="24" t="inlineStr">
+      <c r="E117" s="26" t="inlineStr">
         <is>
           <t>idle</t>
         </is>
       </c>
-      <c r="F117" s="24" t="n">
+      <c r="F117" s="26" t="n">
         <v>2</v>
       </c>
       <c r="G117" s="6" t="n">
@@ -8298,38 +8591,39 @@
       <c r="P117" s="6" t="inlineStr"/>
       <c r="Q117" s="6" t="inlineStr"/>
       <c r="R117" s="6" t="inlineStr"/>
-      <c r="S117" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S117" s="6" t="inlineStr"/>
       <c r="T117" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U117" s="6" t="inlineStr"/>
+      <c r="U117" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V117" s="6" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="24" t="n">
+      <c r="A118" s="26" t="n">
         <v>116</v>
       </c>
-      <c r="B118" s="25">
+      <c r="B118" s="27">
         <f>A118*1000/60</f>
         <v/>
       </c>
-      <c r="C118" s="24" t="inlineStr">
+      <c r="C118" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D118" s="24" t="inlineStr">
+      <c r="D118" s="26" t="inlineStr">
         <is>
           <t>C31</t>
         </is>
       </c>
-      <c r="E118" s="24" t="inlineStr">
+      <c r="E118" s="26" t="inlineStr">
         <is>
           <t>idle</t>
         </is>
       </c>
-      <c r="F118" s="24" t="n">
+      <c r="F118" s="26" t="n">
         <v>3</v>
       </c>
       <c r="G118" s="6" t="n">
@@ -8359,38 +8653,39 @@
       <c r="P118" s="6" t="inlineStr"/>
       <c r="Q118" s="6" t="inlineStr"/>
       <c r="R118" s="6" t="inlineStr"/>
-      <c r="S118" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S118" s="6" t="inlineStr"/>
       <c r="T118" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U118" s="6" t="inlineStr"/>
+      <c r="U118" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V118" s="6" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="24" t="n">
+      <c r="A119" s="26" t="n">
         <v>117</v>
       </c>
-      <c r="B119" s="25">
+      <c r="B119" s="27">
         <f>A119*1000/60</f>
         <v/>
       </c>
-      <c r="C119" s="24" t="inlineStr">
+      <c r="C119" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D119" s="24" t="inlineStr">
+      <c r="D119" s="26" t="inlineStr">
         <is>
           <t>C31</t>
         </is>
       </c>
-      <c r="E119" s="24" t="inlineStr">
+      <c r="E119" s="26" t="inlineStr">
         <is>
           <t>idle</t>
         </is>
       </c>
-      <c r="F119" s="24" t="n">
+      <c r="F119" s="26" t="n">
         <v>4</v>
       </c>
       <c r="G119" s="6" t="n">
@@ -8420,38 +8715,39 @@
       <c r="P119" s="6" t="inlineStr"/>
       <c r="Q119" s="6" t="inlineStr"/>
       <c r="R119" s="6" t="inlineStr"/>
-      <c r="S119" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S119" s="6" t="inlineStr"/>
       <c r="T119" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U119" s="6" t="inlineStr"/>
+      <c r="U119" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V119" s="6" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="24" t="n">
+      <c r="A120" s="26" t="n">
         <v>118</v>
       </c>
-      <c r="B120" s="25">
+      <c r="B120" s="27">
         <f>A120*1000/60</f>
         <v/>
       </c>
-      <c r="C120" s="24" t="inlineStr">
+      <c r="C120" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D120" s="24" t="inlineStr">
+      <c r="D120" s="26" t="inlineStr">
         <is>
           <t>C31</t>
         </is>
       </c>
-      <c r="E120" s="24" t="inlineStr">
+      <c r="E120" s="26" t="inlineStr">
         <is>
           <t>idle</t>
         </is>
       </c>
-      <c r="F120" s="24" t="n">
+      <c r="F120" s="26" t="n">
         <v>5</v>
       </c>
       <c r="G120" s="6" t="n">
@@ -8481,38 +8777,39 @@
       <c r="P120" s="6" t="inlineStr"/>
       <c r="Q120" s="6" t="inlineStr"/>
       <c r="R120" s="6" t="inlineStr"/>
-      <c r="S120" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S120" s="6" t="inlineStr"/>
       <c r="T120" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U120" s="6" t="inlineStr"/>
+      <c r="U120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V120" s="6" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="24" t="n">
+      <c r="A121" s="26" t="n">
         <v>119</v>
       </c>
-      <c r="B121" s="25">
+      <c r="B121" s="27">
         <f>A121*1000/60</f>
         <v/>
       </c>
-      <c r="C121" s="24" t="inlineStr">
+      <c r="C121" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D121" s="24" t="inlineStr">
+      <c r="D121" s="26" t="inlineStr">
         <is>
           <t>C31</t>
         </is>
       </c>
-      <c r="E121" s="24" t="inlineStr">
+      <c r="E121" s="26" t="inlineStr">
         <is>
           <t>idle</t>
         </is>
       </c>
-      <c r="F121" s="24" t="n">
+      <c r="F121" s="26" t="n">
         <v>6</v>
       </c>
       <c r="G121" s="6" t="n">
@@ -8542,38 +8839,39 @@
       <c r="P121" s="6" t="inlineStr"/>
       <c r="Q121" s="6" t="inlineStr"/>
       <c r="R121" s="6" t="inlineStr"/>
-      <c r="S121" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S121" s="6" t="inlineStr"/>
       <c r="T121" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U121" s="6" t="inlineStr"/>
+      <c r="U121" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V121" s="6" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="24" t="n">
+      <c r="A122" s="26" t="n">
         <v>120</v>
       </c>
-      <c r="B122" s="25">
+      <c r="B122" s="27">
         <f>A122*1000/60</f>
         <v/>
       </c>
-      <c r="C122" s="24" t="inlineStr">
+      <c r="C122" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D122" s="24" t="inlineStr">
+      <c r="D122" s="26" t="inlineStr">
         <is>
           <t>C31</t>
         </is>
       </c>
-      <c r="E122" s="24" t="inlineStr">
+      <c r="E122" s="26" t="inlineStr">
         <is>
           <t>idle</t>
         </is>
       </c>
-      <c r="F122" s="24" t="n">
+      <c r="F122" s="26" t="n">
         <v>7</v>
       </c>
       <c r="G122" s="6" t="n">
@@ -8603,38 +8901,39 @@
       <c r="P122" s="6" t="inlineStr"/>
       <c r="Q122" s="6" t="inlineStr"/>
       <c r="R122" s="6" t="inlineStr"/>
-      <c r="S122" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S122" s="6" t="inlineStr"/>
       <c r="T122" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U122" s="6" t="inlineStr"/>
+      <c r="U122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V122" s="6" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="24" t="n">
+      <c r="A123" s="26" t="n">
         <v>121</v>
       </c>
-      <c r="B123" s="25">
+      <c r="B123" s="27">
         <f>A123*1000/60</f>
         <v/>
       </c>
-      <c r="C123" s="24" t="inlineStr">
+      <c r="C123" s="26" t="inlineStr">
         <is>
           <t>F burst จางจนหมด · กลับท่ายืน</t>
         </is>
       </c>
-      <c r="D123" s="24" t="inlineStr">
+      <c r="D123" s="26" t="inlineStr">
         <is>
           <t>C31</t>
         </is>
       </c>
-      <c r="E123" s="24" t="inlineStr">
+      <c r="E123" s="26" t="inlineStr">
         <is>
           <t>idle</t>
         </is>
       </c>
-      <c r="F123" s="24" t="n">
+      <c r="F123" s="26" t="n">
         <v>8</v>
       </c>
       <c r="G123" s="6" t="n">
@@ -8664,13 +8963,14 @@
       <c r="P123" s="6" t="inlineStr"/>
       <c r="Q123" s="6" t="inlineStr"/>
       <c r="R123" s="6" t="inlineStr"/>
-      <c r="S123" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="S123" s="6" t="inlineStr"/>
       <c r="T123" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U123" s="6" t="inlineStr"/>
+      <c r="U123" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V123" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8745,1081 +9045,1081 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="26" t="inlineStr">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>C01</t>
         </is>
       </c>
-      <c r="B2" s="26" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>S2 clip 0</t>
         </is>
       </c>
-      <c r="C2" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="26" t="n">
+      <c r="C2" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="28">
         <f>D2-C2+1</f>
         <v/>
       </c>
-      <c r="F2" s="27">
+      <c r="F2" s="29">
         <f>E2*1000/60</f>
         <v/>
       </c>
-      <c r="G2" s="26" t="n">
+      <c r="G2" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="H2" s="26" t="inlineStr">
+      <c r="H2" s="28" t="inlineStr">
         <is>
           <t>ท่าพร้อม</t>
         </is>
       </c>
-      <c r="I2" s="26" t="inlineStr">
+      <c r="I2" s="28" t="inlineStr">
         <is>
           <t>T000 idle</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="28" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>C02</t>
         </is>
       </c>
-      <c r="B3" s="28" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>S2 clip 1</t>
         </is>
       </c>
-      <c r="C3" s="28" t="n">
+      <c r="C3" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="D3" s="28" t="n">
+      <c r="D3" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="E3" s="28">
+      <c r="E3" s="30">
         <f>D3-C3+1</f>
         <v/>
       </c>
-      <c r="F3" s="29">
+      <c r="F3" s="31">
         <f>E3*1000/60</f>
         <v/>
       </c>
-      <c r="G3" s="28" t="n">
+      <c r="G3" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="H3" s="28" t="inlineStr">
+      <c r="H3" s="30" t="inlineStr">
         <is>
           <t>เริ่มท่า</t>
         </is>
       </c>
-      <c r="I3" s="28" t="inlineStr">
+      <c r="I3" s="30" t="inlineStr">
         <is>
           <t>CAST_START 0.05</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>C03</t>
         </is>
       </c>
-      <c r="B4" s="28" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>S2 clip 2</t>
         </is>
       </c>
-      <c r="C4" s="28" t="n">
+      <c r="C4" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="D4" s="28" t="n">
+      <c r="D4" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="30">
         <f>D4-C4+1</f>
         <v/>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="31">
         <f>E4*1000/60</f>
         <v/>
       </c>
-      <c r="G4" s="28" t="n">
+      <c r="G4" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="H4" s="28" t="inlineStr"/>
-      <c r="I4" s="28" t="inlineStr"/>
+      <c r="H4" s="30" t="inlineStr"/>
+      <c r="I4" s="30" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>C04</t>
         </is>
       </c>
-      <c r="B5" s="28" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>S2 clip 3</t>
         </is>
       </c>
-      <c r="C5" s="28" t="n">
+      <c r="C5" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="D5" s="28" t="n">
+      <c r="D5" s="30" t="n">
         <v>11</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="30">
         <f>D5-C5+1</f>
         <v/>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="31">
         <f>E5*1000/60</f>
         <v/>
       </c>
-      <c r="G5" s="28" t="n">
+      <c r="G5" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="H5" s="28" t="inlineStr"/>
-      <c r="I5" s="28" t="inlineStr"/>
+      <c r="H5" s="30" t="inlineStr"/>
+      <c r="I5" s="30" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>C05</t>
         </is>
       </c>
-      <c r="B6" s="28" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>S2 clip 4</t>
         </is>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="D6" s="28" t="n">
+      <c r="D6" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="30">
         <f>D6-C6+1</f>
         <v/>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="31">
         <f>E6*1000/60</f>
         <v/>
       </c>
-      <c r="G6" s="28" t="n">
+      <c r="G6" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="H6" s="28" t="inlineStr"/>
-      <c r="I6" s="28" t="inlineStr"/>
+      <c r="H6" s="30" t="inlineStr"/>
+      <c r="I6" s="30" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>C06</t>
         </is>
       </c>
-      <c r="B7" s="28" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>S2 clip 5</t>
         </is>
       </c>
-      <c r="C7" s="28" t="n">
+      <c r="C7" s="30" t="n">
         <v>15</v>
       </c>
-      <c r="D7" s="28" t="n">
+      <c r="D7" s="30" t="n">
         <v>17</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="30">
         <f>D7-C7+1</f>
         <v/>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="31">
         <f>E7*1000/60</f>
         <v/>
       </c>
-      <c r="G7" s="28" t="n">
+      <c r="G7" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="H7" s="28" t="inlineStr"/>
-      <c r="I7" s="28" t="inlineStr"/>
+      <c r="H7" s="30" t="inlineStr"/>
+      <c r="I7" s="30" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>C07</t>
         </is>
       </c>
-      <c r="B8" s="28" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>S2 clip 6</t>
         </is>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="30" t="n">
         <v>18</v>
       </c>
-      <c r="D8" s="28" t="n">
+      <c r="D8" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="30">
         <f>D8-C8+1</f>
         <v/>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="31">
         <f>E8*1000/60</f>
         <v/>
       </c>
-      <c r="G8" s="28" t="n">
+      <c r="G8" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="H8" s="28" t="inlineStr"/>
-      <c r="I8" s="28" t="inlineStr"/>
+      <c r="H8" s="30" t="inlineStr"/>
+      <c r="I8" s="30" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="28" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>C08</t>
         </is>
       </c>
-      <c r="B9" s="28" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>S2 clip 7</t>
         </is>
       </c>
-      <c r="C9" s="28" t="n">
+      <c r="C9" s="30" t="n">
         <v>21</v>
       </c>
-      <c r="D9" s="28" t="n">
+      <c r="D9" s="30" t="n">
         <v>23</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="30">
         <f>D9-C9+1</f>
         <v/>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="31">
         <f>E9*1000/60</f>
         <v/>
       </c>
-      <c r="G9" s="28" t="n">
+      <c r="G9" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="H9" s="28" t="inlineStr">
+      <c r="H9" s="30" t="inlineStr">
         <is>
           <t>ง้างไม้</t>
         </is>
       </c>
-      <c r="I9" s="28" t="inlineStr">
+      <c r="I9" s="30" t="inlineStr">
         <is>
           <t>STRIKE_START #1</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>C09</t>
         </is>
       </c>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B10" s="32" t="inlineStr">
         <is>
           <t>S2 clip 8</t>
         </is>
       </c>
-      <c r="C10" s="30" t="n">
+      <c r="C10" s="32" t="n">
         <v>24</v>
       </c>
-      <c r="D10" s="30" t="n">
+      <c r="D10" s="32" t="n">
         <v>29</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="32">
         <f>D10-C10+1</f>
         <v/>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="33">
         <f>E10*1000/60</f>
         <v/>
       </c>
-      <c r="G10" s="30" t="n">
+      <c r="G10" s="32" t="n">
         <v>100</v>
       </c>
-      <c r="H10" s="30" t="inlineStr">
+      <c r="H10" s="32" t="inlineStr">
         <is>
           <t>ตีครั้งที่ 1 (F13)</t>
         </is>
       </c>
-      <c r="I10" s="30" t="inlineStr">
+      <c r="I10" s="32" t="inlineStr">
         <is>
           <t>VFX_SPAWN #0 · GroundHexSpawn ใต้พื้นที่เป้า</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>C10</t>
         </is>
       </c>
-      <c r="B11" s="30" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>S2 clip 9</t>
         </is>
       </c>
-      <c r="C11" s="30" t="n">
+      <c r="C11" s="32" t="n">
         <v>30</v>
       </c>
-      <c r="D11" s="30" t="n">
+      <c r="D11" s="32" t="n">
         <v>32</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="32">
         <f>D11-C11+1</f>
         <v/>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="33">
         <f>E11*1000/60</f>
         <v/>
       </c>
-      <c r="G11" s="30" t="n">
+      <c r="G11" s="32" t="n">
         <v>50</v>
       </c>
-      <c r="H11" s="30" t="inlineStr">
+      <c r="H11" s="32" t="inlineStr">
         <is>
           <t>ค้างท่าตี</t>
         </is>
       </c>
-      <c r="I11" s="30" t="inlineStr"/>
+      <c r="I11" s="32" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="inlineStr">
+      <c r="A12" s="32" t="inlineStr">
         <is>
           <t>C11</t>
         </is>
       </c>
-      <c r="B12" s="30" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>S2 clip 10</t>
         </is>
       </c>
-      <c r="C12" s="30" t="n">
+      <c r="C12" s="32" t="n">
         <v>33</v>
       </c>
-      <c r="D12" s="30" t="n">
+      <c r="D12" s="32" t="n">
         <v>35</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="32">
         <f>D12-C12+1</f>
         <v/>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="33">
         <f>E12*1000/60</f>
         <v/>
       </c>
-      <c r="G12" s="30" t="n">
+      <c r="G12" s="32" t="n">
         <v>50</v>
       </c>
-      <c r="H12" s="30" t="inlineStr"/>
-      <c r="I12" s="30" t="inlineStr"/>
+      <c r="H12" s="32" t="inlineStr"/>
+      <c r="I12" s="32" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>C12</t>
         </is>
       </c>
-      <c r="B13" s="30" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>S2 clip 11</t>
         </is>
       </c>
-      <c r="C13" s="30" t="n">
+      <c r="C13" s="32" t="n">
         <v>36</v>
       </c>
-      <c r="D13" s="30" t="n">
+      <c r="D13" s="32" t="n">
         <v>38</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="32">
         <f>D13-C13+1</f>
         <v/>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="33">
         <f>E13*1000/60</f>
         <v/>
       </c>
-      <c r="G13" s="30" t="n">
+      <c r="G13" s="32" t="n">
         <v>50</v>
       </c>
-      <c r="H13" s="30" t="inlineStr"/>
-      <c r="I13" s="30" t="inlineStr"/>
+      <c r="H13" s="32" t="inlineStr"/>
+      <c r="I13" s="32" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="32" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>C13</t>
         </is>
       </c>
-      <c r="B14" s="32" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>S2 clip 12</t>
         </is>
       </c>
-      <c r="C14" s="32" t="n">
+      <c r="C14" s="34" t="n">
         <v>39</v>
       </c>
-      <c r="D14" s="32" t="n">
+      <c r="D14" s="34" t="n">
         <v>43</v>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="34">
         <f>D14-C14+1</f>
         <v/>
       </c>
-      <c r="F14" s="33">
+      <c r="F14" s="35">
         <f>E14*1000/60</f>
         <v/>
       </c>
-      <c r="G14" s="32" t="n">
+      <c r="G14" s="34" t="n">
         <v>70</v>
       </c>
-      <c r="H14" s="32" t="inlineStr">
+      <c r="H14" s="34" t="inlineStr">
         <is>
           <t>ควงไม้ที่อก</t>
         </is>
       </c>
-      <c r="I14" s="32" t="inlineStr">
+      <c r="I14" s="34" t="inlineStr">
         <is>
           <t>CHARGE_START · GroundHexLoop (ชาร์จ ไม่มีดาเมจ)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>C14</t>
         </is>
       </c>
-      <c r="B15" s="32" t="inlineStr">
+      <c r="B15" s="34" t="inlineStr">
         <is>
           <t>S2 clip 13</t>
         </is>
       </c>
-      <c r="C15" s="32" t="n">
+      <c r="C15" s="34" t="n">
         <v>44</v>
       </c>
-      <c r="D15" s="32" t="n">
+      <c r="D15" s="34" t="n">
         <v>47</v>
       </c>
-      <c r="E15" s="32">
+      <c r="E15" s="34">
         <f>D15-C15+1</f>
         <v/>
       </c>
-      <c r="F15" s="33">
+      <c r="F15" s="35">
         <f>E15*1000/60</f>
         <v/>
       </c>
-      <c r="G15" s="32" t="n">
+      <c r="G15" s="34" t="n">
         <v>70</v>
       </c>
-      <c r="H15" s="32" t="inlineStr"/>
-      <c r="I15" s="32" t="inlineStr"/>
+      <c r="H15" s="34" t="inlineStr"/>
+      <c r="I15" s="34" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="32" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>C15</t>
         </is>
       </c>
-      <c r="B16" s="32" t="inlineStr">
+      <c r="B16" s="34" t="inlineStr">
         <is>
           <t>S2 clip 14</t>
         </is>
       </c>
-      <c r="C16" s="32" t="n">
+      <c r="C16" s="34" t="n">
         <v>48</v>
       </c>
-      <c r="D16" s="32" t="n">
+      <c r="D16" s="34" t="n">
         <v>51</v>
       </c>
-      <c r="E16" s="32">
+      <c r="E16" s="34">
         <f>D16-C16+1</f>
         <v/>
       </c>
-      <c r="F16" s="33">
+      <c r="F16" s="35">
         <f>E16*1000/60</f>
         <v/>
       </c>
-      <c r="G16" s="32" t="n">
+      <c r="G16" s="34" t="n">
         <v>70</v>
       </c>
-      <c r="H16" s="32" t="inlineStr"/>
-      <c r="I16" s="32" t="inlineStr"/>
+      <c r="H16" s="34" t="inlineStr"/>
+      <c r="I16" s="34" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="32" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>C16</t>
         </is>
       </c>
-      <c r="B17" s="32" t="inlineStr">
+      <c r="B17" s="34" t="inlineStr">
         <is>
           <t>S2 clip 15</t>
         </is>
       </c>
-      <c r="C17" s="32" t="n">
+      <c r="C17" s="34" t="n">
         <v>52</v>
       </c>
-      <c r="D17" s="32" t="n">
+      <c r="D17" s="34" t="n">
         <v>55</v>
       </c>
-      <c r="E17" s="32">
+      <c r="E17" s="34">
         <f>D17-C17+1</f>
         <v/>
       </c>
-      <c r="F17" s="33">
+      <c r="F17" s="35">
         <f>E17*1000/60</f>
         <v/>
       </c>
-      <c r="G17" s="32" t="n">
+      <c r="G17" s="34" t="n">
         <v>70</v>
       </c>
-      <c r="H17" s="32" t="inlineStr"/>
-      <c r="I17" s="32" t="inlineStr"/>
+      <c r="H17" s="34" t="inlineStr"/>
+      <c r="I17" s="34" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="32" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>C17</t>
         </is>
       </c>
-      <c r="B18" s="32" t="inlineStr">
+      <c r="B18" s="34" t="inlineStr">
         <is>
           <t>S2 clip 16</t>
         </is>
       </c>
-      <c r="C18" s="32" t="n">
+      <c r="C18" s="34" t="n">
         <v>56</v>
       </c>
-      <c r="D18" s="32" t="n">
+      <c r="D18" s="34" t="n">
         <v>59</v>
       </c>
-      <c r="E18" s="32">
+      <c r="E18" s="34">
         <f>D18-C18+1</f>
         <v/>
       </c>
-      <c r="F18" s="33">
+      <c r="F18" s="35">
         <f>E18*1000/60</f>
         <v/>
       </c>
-      <c r="G18" s="32" t="n">
+      <c r="G18" s="34" t="n">
         <v>70</v>
       </c>
-      <c r="H18" s="32" t="inlineStr"/>
-      <c r="I18" s="32" t="inlineStr"/>
+      <c r="H18" s="34" t="inlineStr"/>
+      <c r="I18" s="34" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="32" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>C18</t>
         </is>
       </c>
-      <c r="B19" s="32" t="inlineStr">
+      <c r="B19" s="34" t="inlineStr">
         <is>
           <t>S2 clip 17</t>
         </is>
       </c>
-      <c r="C19" s="32" t="n">
+      <c r="C19" s="34" t="n">
         <v>60</v>
       </c>
-      <c r="D19" s="32" t="n">
+      <c r="D19" s="34" t="n">
         <v>64</v>
       </c>
-      <c r="E19" s="32">
+      <c r="E19" s="34">
         <f>D19-C19+1</f>
         <v/>
       </c>
-      <c r="F19" s="33">
+      <c r="F19" s="35">
         <f>E19*1000/60</f>
         <v/>
       </c>
-      <c r="G19" s="32" t="n">
+      <c r="G19" s="34" t="n">
         <v>70</v>
       </c>
-      <c r="H19" s="32" t="inlineStr"/>
-      <c r="I19" s="32" t="inlineStr"/>
+      <c r="H19" s="34" t="inlineStr"/>
+      <c r="I19" s="34" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="32" t="inlineStr">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t>C19</t>
         </is>
       </c>
-      <c r="B20" s="32" t="inlineStr">
+      <c r="B20" s="34" t="inlineStr">
         <is>
           <t>S2 clip 18</t>
         </is>
       </c>
-      <c r="C20" s="32" t="n">
+      <c r="C20" s="34" t="n">
         <v>65</v>
       </c>
-      <c r="D20" s="32" t="n">
+      <c r="D20" s="34" t="n">
         <v>67</v>
       </c>
-      <c r="E20" s="32">
+      <c r="E20" s="34">
         <f>D20-C20+1</f>
         <v/>
       </c>
-      <c r="F20" s="33">
+      <c r="F20" s="35">
         <f>E20*1000/60</f>
         <v/>
       </c>
-      <c r="G20" s="32" t="n">
+      <c r="G20" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="H20" s="32" t="inlineStr">
+      <c r="H20" s="34" t="inlineStr">
         <is>
           <t>ยกไม้</t>
         </is>
       </c>
-      <c r="I20" s="32" t="inlineStr"/>
+      <c r="I20" s="34" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="32" t="inlineStr">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t>C20</t>
         </is>
       </c>
-      <c r="B21" s="32" t="inlineStr">
+      <c r="B21" s="34" t="inlineStr">
         <is>
           <t>S2 clip 19</t>
         </is>
       </c>
-      <c r="C21" s="32" t="n">
+      <c r="C21" s="34" t="n">
         <v>68</v>
       </c>
-      <c r="D21" s="32" t="n">
+      <c r="D21" s="34" t="n">
         <v>70</v>
       </c>
-      <c r="E21" s="32">
+      <c r="E21" s="34">
         <f>D21-C21+1</f>
         <v/>
       </c>
-      <c r="F21" s="33">
+      <c r="F21" s="35">
         <f>E21*1000/60</f>
         <v/>
       </c>
-      <c r="G21" s="32" t="n">
+      <c r="G21" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="H21" s="32" t="inlineStr"/>
-      <c r="I21" s="32" t="inlineStr"/>
+      <c r="H21" s="34" t="inlineStr"/>
+      <c r="I21" s="34" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="32" t="inlineStr">
+      <c r="A22" s="34" t="inlineStr">
         <is>
           <t>C21</t>
         </is>
       </c>
-      <c r="B22" s="32" t="inlineStr">
+      <c r="B22" s="34" t="inlineStr">
         <is>
           <t>S2 clip 20</t>
         </is>
       </c>
-      <c r="C22" s="32" t="n">
+      <c r="C22" s="34" t="n">
         <v>71</v>
       </c>
-      <c r="D22" s="32" t="n">
+      <c r="D22" s="34" t="n">
         <v>73</v>
       </c>
-      <c r="E22" s="32">
+      <c r="E22" s="34">
         <f>D22-C22+1</f>
         <v/>
       </c>
-      <c r="F22" s="33">
+      <c r="F22" s="35">
         <f>E22*1000/60</f>
         <v/>
       </c>
-      <c r="G22" s="32" t="n">
+      <c r="G22" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="H22" s="32" t="inlineStr"/>
-      <c r="I22" s="32" t="inlineStr"/>
+      <c r="H22" s="34" t="inlineStr"/>
+      <c r="I22" s="34" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="32" t="inlineStr">
+      <c r="A23" s="34" t="inlineStr">
         <is>
           <t>C22</t>
         </is>
       </c>
-      <c r="B23" s="32" t="inlineStr">
+      <c r="B23" s="34" t="inlineStr">
         <is>
           <t>S2 clip 21</t>
         </is>
       </c>
-      <c r="C23" s="32" t="n">
+      <c r="C23" s="34" t="n">
         <v>74</v>
       </c>
-      <c r="D23" s="32" t="n">
+      <c r="D23" s="34" t="n">
         <v>76</v>
       </c>
-      <c r="E23" s="32">
+      <c r="E23" s="34">
         <f>D23-C23+1</f>
         <v/>
       </c>
-      <c r="F23" s="33">
+      <c r="F23" s="35">
         <f>E23*1000/60</f>
         <v/>
       </c>
-      <c r="G23" s="32" t="n">
+      <c r="G23" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="H23" s="32" t="inlineStr">
+      <c r="H23" s="34" t="inlineStr">
         <is>
           <t>ง้างตีครั้งที่ 2</t>
         </is>
       </c>
-      <c r="I23" s="32" t="inlineStr">
+      <c r="I23" s="34" t="inlineStr">
         <is>
           <t>STRIKE_START #2</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="34" t="inlineStr">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>C23</t>
         </is>
       </c>
-      <c r="B24" s="34" t="inlineStr">
+      <c r="B24" s="36" t="inlineStr">
         <is>
           <t>S2 clip 22</t>
         </is>
       </c>
-      <c r="C24" s="34" t="n">
+      <c r="C24" s="36" t="n">
         <v>77</v>
       </c>
-      <c r="D24" s="34" t="n">
+      <c r="D24" s="36" t="n">
         <v>82</v>
       </c>
-      <c r="E24" s="34">
+      <c r="E24" s="36">
         <f>D24-C24+1</f>
         <v/>
       </c>
-      <c r="F24" s="35">
+      <c r="F24" s="37">
         <f>E24*1000/60</f>
         <v/>
       </c>
-      <c r="G24" s="34" t="n">
+      <c r="G24" s="36" t="n">
         <v>100</v>
       </c>
-      <c r="H24" s="34" t="inlineStr">
+      <c r="H24" s="36" t="inlineStr">
         <is>
           <t>ตีครั้งที่ 2 (F32)</t>
         </is>
       </c>
-      <c r="I24" s="34" t="inlineStr">
+      <c r="I24" s="36" t="inlineStr">
         <is>
           <t>VFX_SPAWN #1 · Loop หยุด · HexActivationBurst</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="34" t="inlineStr">
+      <c r="A25" s="36" t="inlineStr">
         <is>
           <t>C24</t>
         </is>
       </c>
-      <c r="B25" s="34" t="inlineStr">
+      <c r="B25" s="36" t="inlineStr">
         <is>
           <t>S2 clip 23</t>
         </is>
       </c>
-      <c r="C25" s="34" t="n">
+      <c r="C25" s="36" t="n">
         <v>83</v>
       </c>
-      <c r="D25" s="34" t="n">
+      <c r="D25" s="36" t="n">
         <v>87</v>
       </c>
-      <c r="E25" s="34">
+      <c r="E25" s="36">
         <f>D25-C25+1</f>
         <v/>
       </c>
-      <c r="F25" s="35">
+      <c r="F25" s="37">
         <f>E25*1000/60</f>
         <v/>
       </c>
-      <c r="G25" s="34" t="n">
+      <c r="G25" s="36" t="n">
         <v>90</v>
       </c>
-      <c r="H25" s="34" t="inlineStr">
+      <c r="H25" s="36" t="inlineStr">
         <is>
           <t>ค้าง = burst peak</t>
         </is>
       </c>
-      <c r="I25" s="34" t="inlineStr">
+      <c r="I25" s="36" t="inlineStr">
         <is>
           <t>DAMAGE · Slow · ATK/Cast down · Root ถ้ามี Hex Mark</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="36" t="inlineStr">
+      <c r="A26" s="38" t="inlineStr">
         <is>
           <t>C25</t>
         </is>
       </c>
-      <c r="B26" s="36" t="inlineStr">
+      <c r="B26" s="38" t="inlineStr">
         <is>
           <t>S2 clip 24</t>
         </is>
       </c>
-      <c r="C26" s="36" t="n">
+      <c r="C26" s="38" t="n">
         <v>88</v>
       </c>
-      <c r="D26" s="36" t="n">
+      <c r="D26" s="38" t="n">
         <v>91</v>
       </c>
-      <c r="E26" s="36">
+      <c r="E26" s="38">
         <f>D26-C26+1</f>
         <v/>
       </c>
-      <c r="F26" s="37">
+      <c r="F26" s="39">
         <f>E26*1000/60</f>
         <v/>
       </c>
-      <c r="G26" s="36" t="n">
+      <c r="G26" s="38" t="n">
         <v>70</v>
       </c>
-      <c r="H26" s="36" t="inlineStr">
+      <c r="H26" s="38" t="inlineStr">
         <is>
           <t>กลับท่า</t>
         </is>
       </c>
-      <c r="I26" s="36" t="inlineStr">
+      <c r="I26" s="38" t="inlineStr">
         <is>
           <t>RECOVERY_START</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="36" t="inlineStr">
+      <c r="A27" s="38" t="inlineStr">
         <is>
           <t>C26</t>
         </is>
       </c>
-      <c r="B27" s="36" t="inlineStr">
+      <c r="B27" s="38" t="inlineStr">
         <is>
           <t>S2 clip 25</t>
         </is>
       </c>
-      <c r="C27" s="36" t="n">
+      <c r="C27" s="38" t="n">
         <v>92</v>
       </c>
-      <c r="D27" s="36" t="n">
+      <c r="D27" s="38" t="n">
         <v>95</v>
       </c>
-      <c r="E27" s="36">
+      <c r="E27" s="38">
         <f>D27-C27+1</f>
         <v/>
       </c>
-      <c r="F27" s="37">
+      <c r="F27" s="39">
         <f>E27*1000/60</f>
         <v/>
       </c>
-      <c r="G27" s="36" t="n">
+      <c r="G27" s="38" t="n">
         <v>70</v>
       </c>
-      <c r="H27" s="36" t="inlineStr"/>
-      <c r="I27" s="36" t="inlineStr"/>
+      <c r="H27" s="38" t="inlineStr"/>
+      <c r="I27" s="38" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="36" t="inlineStr">
+      <c r="A28" s="38" t="inlineStr">
         <is>
           <t>C27</t>
         </is>
       </c>
-      <c r="B28" s="36" t="inlineStr">
+      <c r="B28" s="38" t="inlineStr">
         <is>
           <t>S2 clip 26</t>
         </is>
       </c>
-      <c r="C28" s="36" t="n">
+      <c r="C28" s="38" t="n">
         <v>96</v>
       </c>
-      <c r="D28" s="36" t="n">
+      <c r="D28" s="38" t="n">
         <v>100</v>
       </c>
-      <c r="E28" s="36">
+      <c r="E28" s="38">
         <f>D28-C28+1</f>
         <v/>
       </c>
-      <c r="F28" s="37">
+      <c r="F28" s="39">
         <f>E28*1000/60</f>
         <v/>
       </c>
-      <c r="G28" s="36" t="n">
+      <c r="G28" s="38" t="n">
         <v>70</v>
       </c>
-      <c r="H28" s="36" t="inlineStr"/>
-      <c r="I28" s="36" t="inlineStr"/>
+      <c r="H28" s="38" t="inlineStr"/>
+      <c r="I28" s="38" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="36" t="inlineStr">
+      <c r="A29" s="38" t="inlineStr">
         <is>
           <t>C28</t>
         </is>
       </c>
-      <c r="B29" s="36" t="inlineStr">
+      <c r="B29" s="38" t="inlineStr">
         <is>
           <t>S2 clip 27</t>
         </is>
       </c>
-      <c r="C29" s="36" t="n">
+      <c r="C29" s="38" t="n">
         <v>101</v>
       </c>
-      <c r="D29" s="36" t="n">
+      <c r="D29" s="38" t="n">
         <v>104</v>
       </c>
-      <c r="E29" s="36">
+      <c r="E29" s="38">
         <f>D29-C29+1</f>
         <v/>
       </c>
-      <c r="F29" s="37">
+      <c r="F29" s="39">
         <f>E29*1000/60</f>
         <v/>
       </c>
-      <c r="G29" s="36" t="n">
+      <c r="G29" s="38" t="n">
         <v>70</v>
       </c>
-      <c r="H29" s="36" t="inlineStr"/>
-      <c r="I29" s="36" t="inlineStr"/>
+      <c r="H29" s="38" t="inlineStr"/>
+      <c r="I29" s="38" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="36" t="inlineStr">
+      <c r="A30" s="38" t="inlineStr">
         <is>
           <t>C29</t>
         </is>
       </c>
-      <c r="B30" s="36" t="inlineStr">
+      <c r="B30" s="38" t="inlineStr">
         <is>
           <t>S2 clip 28</t>
         </is>
       </c>
-      <c r="C30" s="36" t="n">
+      <c r="C30" s="38" t="n">
         <v>105</v>
       </c>
-      <c r="D30" s="36" t="n">
+      <c r="D30" s="38" t="n">
         <v>108</v>
       </c>
-      <c r="E30" s="36">
+      <c r="E30" s="38">
         <f>D30-C30+1</f>
         <v/>
       </c>
-      <c r="F30" s="37">
+      <c r="F30" s="39">
         <f>E30*1000/60</f>
         <v/>
       </c>
-      <c r="G30" s="36" t="n">
+      <c r="G30" s="38" t="n">
         <v>70</v>
       </c>
-      <c r="H30" s="36" t="inlineStr"/>
-      <c r="I30" s="36" t="inlineStr"/>
+      <c r="H30" s="38" t="inlineStr"/>
+      <c r="I30" s="38" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="36" t="inlineStr">
+      <c r="A31" s="38" t="inlineStr">
         <is>
           <t>C30</t>
         </is>
       </c>
-      <c r="B31" s="36" t="inlineStr">
+      <c r="B31" s="38" t="inlineStr">
         <is>
           <t>S2 clip 29</t>
         </is>
       </c>
-      <c r="C31" s="36" t="n">
+      <c r="C31" s="38" t="n">
         <v>109</v>
       </c>
-      <c r="D31" s="36" t="n">
+      <c r="D31" s="38" t="n">
         <v>113</v>
       </c>
-      <c r="E31" s="36">
+      <c r="E31" s="38">
         <f>D31-C31+1</f>
         <v/>
       </c>
-      <c r="F31" s="37">
+      <c r="F31" s="39">
         <f>E31*1000/60</f>
         <v/>
       </c>
-      <c r="G31" s="36" t="n">
+      <c r="G31" s="38" t="n">
         <v>80</v>
       </c>
-      <c r="H31" s="36" t="inlineStr">
+      <c r="H31" s="38" t="inlineStr">
         <is>
           <t>กลับท่ายืน</t>
         </is>
       </c>
-      <c r="I31" s="36" t="inlineStr">
+      <c r="I31" s="38" t="inlineStr">
         <is>
           <t>ท่าจบ</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="36" t="inlineStr">
+      <c r="A32" s="38" t="inlineStr">
         <is>
           <t>C31</t>
         </is>
       </c>
-      <c r="B32" s="36" t="inlineStr">
+      <c r="B32" s="38" t="inlineStr">
         <is>
           <t>idle</t>
         </is>
       </c>
-      <c r="C32" s="36" t="n">
+      <c r="C32" s="38" t="n">
         <v>114</v>
       </c>
-      <c r="D32" s="36" t="n">
+      <c r="D32" s="38" t="n">
         <v>121</v>
       </c>
-      <c r="E32" s="36">
+      <c r="E32" s="38">
         <f>D32-C32+1</f>
         <v/>
       </c>
-      <c r="F32" s="37">
+      <c r="F32" s="39">
         <f>E32*1000/60</f>
         <v/>
       </c>
-      <c r="G32" s="36" t="inlineStr"/>
-      <c r="H32" s="36" t="inlineStr">
+      <c r="G32" s="38" t="inlineStr"/>
+      <c r="H32" s="38" t="inlineStr">
         <is>
           <t>idle</t>
         </is>
       </c>
-      <c r="I32" s="36" t="inlineStr">
+      <c r="I32" s="38" t="inlineStr">
         <is>
           <t>ต่อ idle</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="D33" s="38" t="inlineStr">
+      <c r="D33" s="40" t="inlineStr">
         <is>
           <t>รวม</t>
         </is>
       </c>
-      <c r="E33" s="38">
+      <c r="E33" s="40">
         <f>SUM(E2:E32)</f>
         <v/>
       </c>
-      <c r="F33" s="39">
+      <c r="F33" s="41">
         <f>SUM(F2:F32)</f>
         <v/>
       </c>
-      <c r="G33" s="38">
+      <c r="G33" s="40">
         <f>SUM(G2:G32)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="40" t="inlineStr">
+      <c r="A34" s="42" t="inlineStr">
         <is>
           <t>Game ms = steps ของท่า skill2 ใน SHEETS hero-mordrienne.png · VFX วางบนพื้นกลางพื้นที่ 2 × 2 (SQUARE_2) จุดเดียวกันทั้ง 3 ชั้น</t>
         </is>
@@ -9836,7 +10136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9892,160 +10192,202 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="41" t="inlineStr">
+      <c r="A2" s="43" t="inlineStr">
         <is>
           <t>spawn</t>
         </is>
       </c>
-      <c r="B2" s="42" t="inlineStr">
+      <c r="B2" s="44" t="inlineStr">
         <is>
           <t>Hex Spawn</t>
         </is>
       </c>
-      <c r="C2" s="42" t="inlineStr">
+      <c r="C2" s="44" t="inlineStr">
         <is>
           <t>fx-mordrienne-s2-spawn (9 × 27.8 ms)</t>
         </is>
       </c>
-      <c r="D2" s="42" t="inlineStr">
+      <c r="D2" s="44" t="inlineStr">
         <is>
           <t>024–039</t>
         </is>
       </c>
-      <c r="E2" s="42" t="inlineStr">
+      <c r="E2" s="44" t="inlineStr">
         <is>
           <t>1, 2, 3, 4, 5, 6, 7, 8, 9</t>
         </is>
       </c>
-      <c r="F2" s="42" t="inlineStr">
+      <c r="F2" s="44" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G2" s="42" t="inlineStr">
+      <c r="G2" s="44" t="inlineStr">
         <is>
           <t>กลางพื้นที่ 2 × 2 บนพื้น</t>
         </is>
       </c>
-      <c r="H2" s="42" t="inlineStr">
+      <c r="H2" s="44" t="inlineStr">
         <is>
           <t>T024 วงเล็ก → วงเต็ม f7 → T038 จบพอดีตอนควง</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="43" t="inlineStr">
+      <c r="A3" s="45" t="inlineStr">
         <is>
           <t>loop</t>
         </is>
       </c>
-      <c r="B3" s="42" t="inlineStr">
+      <c r="B3" s="44" t="inlineStr">
         <is>
           <t>Hex Loop</t>
         </is>
       </c>
-      <c r="C3" s="42" t="inlineStr">
+      <c r="C3" s="44" t="inlineStr">
         <is>
           <t>fx-mordrienne-s2-loop (8 × 77.5 ms)</t>
         </is>
       </c>
-      <c r="D3" s="42" t="inlineStr">
+      <c r="D3" s="44" t="inlineStr">
         <is>
           <t>039–076</t>
         </is>
       </c>
-      <c r="E3" s="42" t="inlineStr">
+      <c r="E3" s="44" t="inlineStr">
         <is>
           <t>1, 2, 3, 4, 5, 6, 7, 8</t>
         </is>
       </c>
-      <c r="F3" s="42" t="inlineStr">
+      <c r="F3" s="44" t="inlineStr">
         <is>
           <t>under</t>
         </is>
       </c>
-      <c r="G3" s="42" t="inlineStr">
+      <c r="G3" s="44" t="inlineStr">
         <is>
           <t>จุดเดียวกัน</t>
         </is>
       </c>
-      <c r="H3" s="42" t="inlineStr">
+      <c r="H3" s="44" t="inlineStr">
         <is>
           <t>T039 → T075 หนึ่งรอบหายใจ · หยุดทันทีที่ตีครั้งที่ 2</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="44" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>burst</t>
         </is>
       </c>
-      <c r="B4" s="42" t="inlineStr">
+      <c r="B4" s="44" t="inlineStr">
         <is>
           <t>Activation Burst</t>
         </is>
       </c>
-      <c r="C4" s="42" t="inlineStr">
+      <c r="C4" s="44" t="inlineStr">
         <is>
           <t>fx-mordrienne-s2-burst (8 × 50 ms + fade 150)</t>
         </is>
       </c>
-      <c r="D4" s="42" t="inlineStr">
+      <c r="D4" s="44" t="inlineStr">
         <is>
           <t>077–109</t>
         </is>
       </c>
-      <c r="E4" s="42" t="inlineStr">
+      <c r="E4" s="44" t="inlineStr">
         <is>
           <t>1, 2, 3, 4, 5, 6, 7, 8</t>
         </is>
       </c>
-      <c r="F4" s="42" t="inlineStr">
+      <c r="F4" s="44" t="inlineStr">
         <is>
           <t>over</t>
         </is>
       </c>
-      <c r="G4" s="42" t="inlineStr">
+      <c r="G4" s="44" t="inlineStr">
         <is>
           <t>จุดเดียวกัน</t>
         </is>
       </c>
-      <c r="H4" s="42" t="inlineStr">
+      <c r="H4" s="44" t="inlineStr">
         <is>
           <t>T076 ปะทุ → peak f3 T082 = ดาเมจ → สลาย f8 → หมด T109</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="45" t="inlineStr">
+      <c r="A5" s="47" t="inlineStr">
+        <is>
+          <t>tip</t>
+        </is>
+      </c>
+      <c r="B5" s="44" t="inlineStr">
+        <is>
+          <t>Wand Flash</t>
+        </is>
+      </c>
+      <c r="C5" s="44" t="inlineStr">
+        <is>
+          <t>fx-mordrienne-s2-tip (7 × 35 ms + fade 80)</t>
+        </is>
+      </c>
+      <c r="D5" s="44" t="inlineStr">
+        <is>
+          <t>024–043, 077–095</t>
+        </is>
+      </c>
+      <c r="E5" s="44" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
+      <c r="F5" s="44" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="G5" s="44" t="inlineStr">
+        <is>
+          <t>ปลายคทาท่าตี</t>
+        </is>
+      </c>
+      <c r="H5" s="44" t="inlineStr">
+        <is>
+          <t>แสงเขียวที่ปลายคทาตอนตีทั้ง 2 ครั้ง T024 / T076</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="48" t="inlineStr">
         <is>
           <t>events</t>
         </is>
       </c>
-      <c r="B5" s="42" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>อีเวนต์</t>
         </is>
       </c>
-      <c r="C5" s="42" t="inlineStr">
+      <c r="C6" s="44" t="inlineStr">
         <is>
           <t>engine</t>
         </is>
       </c>
-      <c r="D5" s="42" t="inlineStr"/>
-      <c r="E5" s="42" t="inlineStr"/>
-      <c r="F5" s="42" t="inlineStr">
+      <c r="D6" s="44" t="inlineStr"/>
+      <c r="E6" s="44" t="inlineStr"/>
+      <c r="F6" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G5" s="42" t="inlineStr">
+      <c r="G6" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H5" s="42" t="inlineStr">
+      <c r="H6" s="44" t="inlineStr">
         <is>
           <t>DAMAGE ครั้งเดียวที่ burst peak · ไม่มี impact VFX ซ้ำ</t>
         </is>
@@ -10094,209 +10436,209 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" s="47">
+      <c r="A2" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" s="50">
         <f>A2*1000/60</f>
         <v/>
       </c>
-      <c r="C2" s="46" t="inlineStr">
+      <c r="C2" s="49" t="inlineStr">
         <is>
           <t>IDLE</t>
         </is>
       </c>
-      <c r="D2" s="46" t="inlineStr">
+      <c r="D2" s="49" t="inlineStr">
         <is>
           <t>C01</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="46" t="n">
+      <c r="A3" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="B3" s="47">
+      <c r="B3" s="50">
         <f>A3*1000/60</f>
         <v/>
       </c>
-      <c r="C3" s="46" t="inlineStr">
+      <c r="C3" s="49" t="inlineStr">
         <is>
           <t>CAST_START</t>
         </is>
       </c>
-      <c r="D3" s="46" t="inlineStr">
+      <c r="D3" s="49" t="inlineStr">
         <is>
           <t>C02 เริ่มท่า</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="46" t="n">
+      <c r="A4" s="49" t="n">
         <v>21</v>
       </c>
-      <c r="B4" s="47">
+      <c r="B4" s="50">
         <f>A4*1000/60</f>
         <v/>
       </c>
-      <c r="C4" s="46" t="inlineStr">
+      <c r="C4" s="49" t="inlineStr">
         <is>
           <t>STRIKE_START #1</t>
         </is>
       </c>
-      <c r="D4" s="46" t="inlineStr">
+      <c r="D4" s="49" t="inlineStr">
         <is>
           <t>C08</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="46" t="n">
+      <c r="A5" s="49" t="n">
         <v>24</v>
       </c>
-      <c r="B5" s="47">
+      <c r="B5" s="50">
         <f>A5*1000/60</f>
         <v/>
       </c>
-      <c r="C5" s="46" t="inlineStr">
+      <c r="C5" s="49" t="inlineStr">
         <is>
           <t>STRIKE 1 · HEX SPAWN</t>
         </is>
       </c>
-      <c r="D5" s="46" t="inlineStr">
+      <c r="D5" s="49" t="inlineStr">
         <is>
           <t>C09 · วงเฮ็กซ์เกิดบนพื้น (ไม่ติดตัว)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="46" t="n">
+      <c r="A6" s="49" t="n">
         <v>39</v>
       </c>
-      <c r="B6" s="47">
+      <c r="B6" s="50">
         <f>A6*1000/60</f>
         <v/>
       </c>
-      <c r="C6" s="46" t="inlineStr">
+      <c r="C6" s="49" t="inlineStr">
         <is>
           <t>CHARGE_START · HEX LOOP</t>
         </is>
       </c>
-      <c r="D6" s="46" t="inlineStr">
+      <c r="D6" s="49" t="inlineStr">
         <is>
           <t>C13 ควงไม้ · วงชาร์จ</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="46" t="n">
+      <c r="A7" s="49" t="n">
         <v>73</v>
       </c>
-      <c r="B7" s="47">
+      <c r="B7" s="50">
         <f>A7*1000/60</f>
         <v/>
       </c>
-      <c r="C7" s="46" t="inlineStr">
+      <c r="C7" s="49" t="inlineStr">
         <is>
           <t>STRIKE_START #2</t>
         </is>
       </c>
-      <c r="D7" s="46" t="inlineStr">
+      <c r="D7" s="49" t="inlineStr">
         <is>
           <t>C22</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="46" t="n">
+      <c r="A8" s="49" t="n">
         <v>76</v>
       </c>
-      <c r="B8" s="47">
+      <c r="B8" s="50">
         <f>A8*1000/60</f>
         <v/>
       </c>
-      <c r="C8" s="46" t="inlineStr">
+      <c r="C8" s="49" t="inlineStr">
         <is>
           <t>STRIKE 2 · ACTIVATION</t>
         </is>
       </c>
-      <c r="D8" s="46" t="inlineStr">
+      <c r="D8" s="49" t="inlineStr">
         <is>
           <t>C23 · loop หยุดทันที · burst เกิด</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="48" t="n">
+      <c r="A9" s="51" t="n">
         <v>82</v>
       </c>
-      <c r="B9" s="49">
+      <c r="B9" s="52">
         <f>A9*1000/60</f>
         <v/>
       </c>
-      <c r="C9" s="48" t="inlineStr">
+      <c r="C9" s="51" t="inlineStr">
         <is>
           <t>DAMAGE (magic AoE)</t>
         </is>
       </c>
-      <c r="D9" s="48" t="inlineStr">
+      <c r="D9" s="51" t="inlineStr">
         <is>
           <t>burst peak f3</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="46" t="n">
+      <c r="A10" s="49" t="n">
         <v>82</v>
       </c>
-      <c r="B10" s="47">
+      <c r="B10" s="50">
         <f>A10*1000/60</f>
         <v/>
       </c>
-      <c r="C10" s="46" t="inlineStr">
+      <c r="C10" s="49" t="inlineStr">
         <is>
           <t>SLOW · ATK/CAST DOWN · ROOT*</t>
         </is>
       </c>
-      <c r="D10" s="46" t="inlineStr">
+      <c r="D10" s="49" t="inlineStr">
         <is>
           <t>*เฉพาะเป้าที่ติด Hex Mark</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="46" t="n">
+      <c r="A11" s="49" t="n">
         <v>88</v>
       </c>
-      <c r="B11" s="47">
+      <c r="B11" s="50">
         <f>A11*1000/60</f>
         <v/>
       </c>
-      <c r="C11" s="46" t="inlineStr">
+      <c r="C11" s="49" t="inlineStr">
         <is>
           <t>RECOVERY_START</t>
         </is>
       </c>
-      <c r="D11" s="46" t="inlineStr">
+      <c r="D11" s="49" t="inlineStr">
         <is>
           <t>C25</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="46" t="n">
+      <c r="A12" s="49" t="n">
         <v>113</v>
       </c>
-      <c r="B12" s="47">
+      <c r="B12" s="50">
         <f>A12*1000/60</f>
         <v/>
       </c>
-      <c r="C12" s="46" t="inlineStr">
+      <c r="C12" s="49" t="inlineStr">
         <is>
           <t>IDLE</t>
         </is>
       </c>
-      <c r="D12" s="46" t="inlineStr">
+      <c r="D12" s="49" t="inlineStr">
         <is>
           <t>clip end 1.89s</t>
         </is>
@@ -10313,7 +10655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10333,56 +10675,68 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="50" t="inlineStr">
+      <c r="A2" s="53" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="B2" s="50" t="inlineStr">
+      <c r="B2" s="53" t="inlineStr">
         <is>
           <t>Hex Spawn / Loop (ใต้ตัวละคร)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="50" t="inlineStr">
+      <c r="A3" s="53" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="B3" s="50" t="inlineStr">
+      <c r="B3" s="53" t="inlineStr">
         <is>
           <t>ตัวละคร (L1)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="50" t="inlineStr">
+      <c r="A4" s="53" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="B4" s="50" t="inlineStr">
+      <c r="B4" s="53" t="inlineStr">
         <is>
           <t>Activation Burst (L4)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="50" t="inlineStr">
+      <c r="A5" s="53" t="inlineStr">
         <is>
           <t>L4</t>
         </is>
       </c>
-      <c r="B5" s="50" t="inlineStr">
-        <is>
-          <t>อีเวนต์ (L5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" s="51" t="inlineStr">
+      <c r="B5" s="53" t="inlineStr">
+        <is>
+          <t>Wand-tip Flash (L5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="53" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="B6" s="53" t="inlineStr">
+        <is>
+          <t>อีเวนต์ (L6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" s="54" t="inlineStr">
         <is>
           <t>หน้าตัวละครกับปลายอาวุธถูกเว้นออกจาก L5 ทุกเฟรม (เอฟเฟกต์ไม่บังหน้า/ปลายอาวุธ)</t>
         </is>
